--- a/data/Base_prix_CI_complet.xlsx
+++ b/data/Base_prix_CI_complet.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M260"/>
+  <dimension ref="A1:M280"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>INS-01</v>
       </c>
       <c r="B2" t="str">
-        <v>Levés topographiques</v>
+        <v>"Levés topographiques"</v>
       </c>
       <c r="C2" t="str">
         <v>Installation de chantier</v>
@@ -456,17 +456,17 @@
       <c r="E2" t="str">
         <v>ha</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>229594</v>
       </c>
       <c r="G2" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H2" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I2" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J2" t="str">
         <v>14/10/2026</v>
@@ -486,7 +486,7 @@
         <v>INS-02</v>
       </c>
       <c r="B3" t="str">
-        <v>Implantation des ouvrages</v>
+        <v>"Implantation des ouvrages"</v>
       </c>
       <c r="C3" t="str">
         <v>Installation de chantier</v>
@@ -497,17 +497,17 @@
       <c r="E3" t="str">
         <v>ml</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <v>2488</v>
       </c>
       <c r="G3" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H3" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I3" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J3" t="str">
         <v>14/10/2026</v>
@@ -527,7 +527,7 @@
         <v>INS-03</v>
       </c>
       <c r="B4" t="str">
-        <v>Clôture en tôle ondulée, h = 2 m</v>
+        <v>"Clôture en tôle ondulée, h = 2 m"</v>
       </c>
       <c r="C4" t="str">
         <v>Installation de chantier</v>
@@ -538,17 +538,17 @@
       <c r="E4" t="str">
         <v>ml</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
         <v>23801</v>
       </c>
       <c r="G4" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H4" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I4" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J4" t="str">
         <v>14/10/2026</v>
@@ -568,7 +568,7 @@
         <v>INS-04</v>
       </c>
       <c r="B5" t="str">
-        <v>Clôture en planche, h = 2 m</v>
+        <v>"Clôture en planche, h = 2 m"</v>
       </c>
       <c r="C5" t="str">
         <v>Installation de chantier</v>
@@ -579,17 +579,17 @@
       <c r="E5" t="str">
         <v>ml</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
         <v>36256</v>
       </c>
       <c r="G5" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H5" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I5" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J5" t="str">
         <v>14/10/2026</v>
@@ -609,7 +609,7 @@
         <v>INS-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Location conteneur aménagé 20 pieds (3 mois min., hors transport)</v>
+        <v>"Location conteneur aménagé 20 pieds (3 mois min., hors transport)"</v>
       </c>
       <c r="C6" t="str">
         <v>Installation de chantier</v>
@@ -620,17 +620,17 @@
       <c r="E6" t="str">
         <v>mois</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
         <v>300000</v>
       </c>
       <c r="G6" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H6" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I6" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J6" t="str">
         <v>14/10/2026</v>
@@ -650,7 +650,7 @@
         <v>INS-06</v>
       </c>
       <c r="B7" t="str">
-        <v>Location conteneur aménagé 40 pieds (3 mois min., hors transport)</v>
+        <v>"Location conteneur aménagé 40 pieds (3 mois min., hors transport)"</v>
       </c>
       <c r="C7" t="str">
         <v>Installation de chantier</v>
@@ -661,17 +661,17 @@
       <c r="E7" t="str">
         <v>mois</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="str">
         <v>350000</v>
       </c>
       <c r="G7" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H7" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I7" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J7" t="str">
         <v>14/10/2026</v>
@@ -691,7 +691,7 @@
         <v>INS-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Achat conteneur aménagé 20 pieds</v>
+        <v>"Achat conteneur aménagé 20 pieds"</v>
       </c>
       <c r="C8" t="str">
         <v>Installation de chantier</v>
@@ -702,17 +702,17 @@
       <c r="E8" t="str">
         <v>u</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="str">
         <v>3300000</v>
       </c>
       <c r="G8" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H8" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I8" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J8" t="str">
         <v>14/10/2026</v>
@@ -732,7 +732,7 @@
         <v>INS-08</v>
       </c>
       <c r="B9" t="str">
-        <v>Achat conteneur aménagé 40 pieds</v>
+        <v>"Achat conteneur aménagé 40 pieds"</v>
       </c>
       <c r="C9" t="str">
         <v>Installation de chantier</v>
@@ -743,17 +743,17 @@
       <c r="E9" t="str">
         <v>u</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="str">
         <v>5500000</v>
       </c>
       <c r="G9" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H9" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I9" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J9" t="str">
         <v>14/10/2026</v>
@@ -773,7 +773,7 @@
         <v>INS-09</v>
       </c>
       <c r="B10" t="str">
-        <v>Location sanitaire de chantier (1 WC, 1 douche, lavabo)</v>
+        <v>"Location sanitaire de chantier (1 WC, 1 douche, lavabo)"</v>
       </c>
       <c r="C10" t="str">
         <v>Installation de chantier</v>
@@ -784,17 +784,17 @@
       <c r="E10" t="str">
         <v>mois</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="str">
         <v>100000</v>
       </c>
       <c r="G10" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H10" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I10" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J10" t="str">
         <v>14/10/2026</v>
@@ -814,7 +814,7 @@
         <v>INS-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Branchement électricité (CIE), forfait</v>
+        <v>"Branchement électricité (CIE), forfait"</v>
       </c>
       <c r="C11" t="str">
         <v>Réseaux</v>
@@ -825,17 +825,17 @@
       <c r="E11" t="str">
         <v>forfait</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="str">
         <v>125000</v>
       </c>
       <c r="G11" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H11" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I11" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J11" t="str">
         <v>14/10/2026</v>
@@ -855,7 +855,7 @@
         <v>INS-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Branchement eau (SODECI), forfait</v>
+        <v>"Branchement eau (SODECI), forfait"</v>
       </c>
       <c r="C12" t="str">
         <v>Réseaux</v>
@@ -866,17 +866,17 @@
       <c r="E12" t="str">
         <v>forfait</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="str">
         <v>250780</v>
       </c>
       <c r="G12" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H12" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I12" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J12" t="str">
         <v>14/10/2026</v>
@@ -896,7 +896,7 @@
         <v>INS-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Branchement téléphone (Orange), forfait</v>
+        <v>"Branchement téléphone (Orange), forfait"</v>
       </c>
       <c r="C13" t="str">
         <v>Réseaux</v>
@@ -907,17 +907,17 @@
       <c r="E13" t="str">
         <v>forfait</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="str">
         <v>47104</v>
       </c>
       <c r="G13" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H13" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I13" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J13" t="str">
         <v>14/10/2026</v>
@@ -937,7 +937,7 @@
         <v>INS-13</v>
       </c>
       <c r="B14" t="str">
-        <v>Ponceau planche pour véhicule léger</v>
+        <v>"Ponceau planche pour véhicule léger"</v>
       </c>
       <c r="C14" t="str">
         <v>Voirie</v>
@@ -948,17 +948,17 @@
       <c r="E14" t="str">
         <v>u</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="str">
         <v>38488</v>
       </c>
       <c r="G14" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H14" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I14" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J14" t="str">
         <v>14/10/2026</v>
@@ -978,7 +978,7 @@
         <v>INS-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Voie d'accès en tout-venant, épaisseur 10 cm</v>
+        <v>"Voie d'accès en tout-venant, épaisseur 10 cm"</v>
       </c>
       <c r="C15" t="str">
         <v>Voirie</v>
@@ -989,17 +989,17 @@
       <c r="E15" t="str">
         <v>m2</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="str">
         <v>1797</v>
       </c>
       <c r="G15" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H15" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I15" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J15" t="str">
         <v>14/10/2026</v>
@@ -1019,7 +1019,7 @@
         <v>MAT-01</v>
       </c>
       <c r="B16" t="str">
-        <v>Location camion-benne (Abidjan)</v>
+        <v>"Location camion-benne (Abidjan)"</v>
       </c>
       <c r="C16" t="str">
         <v>Matériel</v>
@@ -1030,17 +1030,17 @@
       <c r="E16" t="str">
         <v>jour</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="str">
         <v>100000</v>
       </c>
       <c r="G16" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H16" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I16" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J16" t="str">
         <v>14/10/2026</v>
@@ -1060,7 +1060,7 @@
         <v>MAT-02</v>
       </c>
       <c r="B17" t="str">
-        <v>Location camion-benne (hors Abidjan)</v>
+        <v>"Location camion-benne (hors Abidjan)"</v>
       </c>
       <c r="C17" t="str">
         <v>Matériel</v>
@@ -1071,17 +1071,17 @@
       <c r="E17" t="str">
         <v>jour</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="str">
         <v>120000</v>
       </c>
       <c r="G17" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H17" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I17" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J17" t="str">
         <v>14/10/2026</v>
@@ -1101,7 +1101,7 @@
         <v>MAT-03</v>
       </c>
       <c r="B18" t="str">
-        <v>Location chargeuse</v>
+        <v>"Location chargeuse"</v>
       </c>
       <c r="C18" t="str">
         <v>Matériel</v>
@@ -1112,17 +1112,17 @@
       <c r="E18" t="str">
         <v>jour</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="str">
         <v>150000</v>
       </c>
       <c r="G18" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H18" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I18" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J18" t="str">
         <v>14/10/2026</v>
@@ -1142,7 +1142,7 @@
         <v>MAT-04</v>
       </c>
       <c r="B19" t="str">
-        <v>Location niveleuse (grader 12G)</v>
+        <v>"Location niveleuse (grader 12G)"</v>
       </c>
       <c r="C19" t="str">
         <v>Matériel</v>
@@ -1153,17 +1153,17 @@
       <c r="E19" t="str">
         <v>jour</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="str">
         <v>160000</v>
       </c>
       <c r="G19" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H19" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I19" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J19" t="str">
         <v>14/10/2026</v>
@@ -1183,7 +1183,7 @@
         <v>MAT-05</v>
       </c>
       <c r="B20" t="str">
-        <v>Location compacteur à rouleau vibrant, guidage manuel</v>
+        <v>"Location compacteur à rouleau vibrant, guidage manuel"</v>
       </c>
       <c r="C20" t="str">
         <v>Matériel</v>
@@ -1194,17 +1194,17 @@
       <c r="E20" t="str">
         <v>jour</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="str">
         <v>50000</v>
       </c>
       <c r="G20" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H20" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I20" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J20" t="str">
         <v>14/10/2026</v>
@@ -1224,7 +1224,7 @@
         <v>MAT-06</v>
       </c>
       <c r="B21" t="str">
-        <v>Location compacteur à rouleau vibrant</v>
+        <v>"Location compacteur à rouleau vibrant"</v>
       </c>
       <c r="C21" t="str">
         <v>Matériel</v>
@@ -1235,17 +1235,17 @@
       <c r="E21" t="str">
         <v>jour</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="str">
         <v>160000</v>
       </c>
       <c r="G21" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H21" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I21" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J21" t="str">
         <v>14/10/2026</v>
@@ -1265,7 +1265,7 @@
         <v>MAT-07</v>
       </c>
       <c r="B22" t="str">
-        <v>Location mini-pelle à chenille (avec godet)</v>
+        <v>"Location mini-pelle à chenille (avec godet)"</v>
       </c>
       <c r="C22" t="str">
         <v>Matériel</v>
@@ -1276,17 +1276,17 @@
       <c r="E22" t="str">
         <v>jour</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="str">
         <v>120000</v>
       </c>
       <c r="G22" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H22" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I22" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J22" t="str">
         <v>14/10/2026</v>
@@ -1306,7 +1306,7 @@
         <v>MAT-08</v>
       </c>
       <c r="B23" t="str">
-        <v>Location pelle hydraulique à chenille 320</v>
+        <v>"Location pelle hydraulique à chenille 320"</v>
       </c>
       <c r="C23" t="str">
         <v>Matériel</v>
@@ -1317,17 +1317,17 @@
       <c r="E23" t="str">
         <v>jour</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="str">
         <v>300000</v>
       </c>
       <c r="G23" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H23" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I23" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J23" t="str">
         <v>14/10/2026</v>
@@ -1347,7 +1347,7 @@
         <v>MAT-09</v>
       </c>
       <c r="B24" t="str">
-        <v>Location plaque vibrante</v>
+        <v>"Location plaque vibrante"</v>
       </c>
       <c r="C24" t="str">
         <v>Matériel</v>
@@ -1358,17 +1358,17 @@
       <c r="E24" t="str">
         <v>jour</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="str">
         <v>50000</v>
       </c>
       <c r="G24" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H24" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I24" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J24" t="str">
         <v>14/10/2026</v>
@@ -1388,7 +1388,7 @@
         <v>MAT-10</v>
       </c>
       <c r="B25" t="str">
-        <v>Location tractopelle à chenille (avec godet)</v>
+        <v>"Location tractopelle à chenille (avec godet)"</v>
       </c>
       <c r="C25" t="str">
         <v>Matériel</v>
@@ -1399,17 +1399,17 @@
       <c r="E25" t="str">
         <v>jour</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="str">
         <v>120000</v>
       </c>
       <c r="G25" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H25" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I25" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J25" t="str">
         <v>14/10/2026</v>
@@ -1429,7 +1429,7 @@
         <v>MAT-11</v>
       </c>
       <c r="B26" t="str">
-        <v>Location bétonnière 350 L</v>
+        <v>"Location bétonnière 350 L"</v>
       </c>
       <c r="C26" t="str">
         <v>Matériel</v>
@@ -1440,17 +1440,17 @@
       <c r="E26" t="str">
         <v>mois</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="str">
         <v>50000</v>
       </c>
       <c r="G26" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H26" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I26" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J26" t="str">
         <v>14/10/2026</v>
@@ -1470,7 +1470,7 @@
         <v>MAT-12</v>
       </c>
       <c r="B27" t="str">
-        <v>Location compresseur</v>
+        <v>"Location compresseur"</v>
       </c>
       <c r="C27" t="str">
         <v>Matériel</v>
@@ -1481,17 +1481,17 @@
       <c r="E27" t="str">
         <v>jour</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="str">
         <v>25000</v>
       </c>
       <c r="G27" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H27" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I27" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J27" t="str">
         <v>14/10/2026</v>
@@ -1511,7 +1511,7 @@
         <v>MAT-13</v>
       </c>
       <c r="B28" t="str">
-        <v>Location motopompe</v>
+        <v>"Location motopompe"</v>
       </c>
       <c r="C28" t="str">
         <v>Matériel</v>
@@ -1522,17 +1522,17 @@
       <c r="E28" t="str">
         <v>jour</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="str">
         <v>10000</v>
       </c>
       <c r="G28" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H28" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I28" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J28" t="str">
         <v>14/10/2026</v>
@@ -1552,7 +1552,7 @@
         <v>MAT-14</v>
       </c>
       <c r="B29" t="str">
-        <v>Location aiguille vibrante, électrique</v>
+        <v>"Location aiguille vibrante, électrique"</v>
       </c>
       <c r="C29" t="str">
         <v>Matériel</v>
@@ -1563,17 +1563,17 @@
       <c r="E29" t="str">
         <v>jour</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="str">
         <v>5000</v>
       </c>
       <c r="G29" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H29" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I29" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J29" t="str">
         <v>14/10/2026</v>
@@ -1593,7 +1593,7 @@
         <v>MAT-15</v>
       </c>
       <c r="B30" t="str">
-        <v>Location aiguille vibrante, avec compresseur</v>
+        <v>"Location aiguille vibrante, avec compresseur"</v>
       </c>
       <c r="C30" t="str">
         <v>Matériel</v>
@@ -1604,17 +1604,17 @@
       <c r="E30" t="str">
         <v>jour</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="str">
         <v>5000</v>
       </c>
       <c r="G30" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H30" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I30" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J30" t="str">
         <v>14/10/2026</v>
@@ -1634,7 +1634,7 @@
         <v>MAT-16</v>
       </c>
       <c r="B31" t="str">
-        <v>Location nacelle traditionnelle (hors montage)</v>
+        <v>"Location nacelle traditionnelle (hors montage)"</v>
       </c>
       <c r="C31" t="str">
         <v>Matériel</v>
@@ -1645,17 +1645,17 @@
       <c r="E31" t="str">
         <v>jour</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="str">
         <v>35000</v>
       </c>
       <c r="G31" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H31" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I31" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J31" t="str">
         <v>14/10/2026</v>
@@ -1675,7 +1675,7 @@
         <v>MAT-17</v>
       </c>
       <c r="B32" t="str">
-        <v>Achat nacelle traditionnelle</v>
+        <v>"Achat nacelle traditionnelle"</v>
       </c>
       <c r="C32" t="str">
         <v>Matériel</v>
@@ -1686,17 +1686,17 @@
       <c r="E32" t="str">
         <v>u</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="str">
         <v>1500000</v>
       </c>
       <c r="G32" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H32" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I32" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J32" t="str">
         <v>14/10/2026</v>
@@ -1716,7 +1716,7 @@
         <v>COF-01</v>
       </c>
       <c r="B33" t="str">
-        <v>Location simple banche métallique (coffrage)</v>
+        <v>"Location simple banche métallique (coffrage)"</v>
       </c>
       <c r="C33" t="str">
         <v>Coffrage</v>
@@ -1727,17 +1727,17 @@
       <c r="E33" t="str">
         <v>m2</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="str">
         <v>5500</v>
       </c>
       <c r="G33" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H33" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I33" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J33" t="str">
         <v>14/10/2026</v>
@@ -1757,7 +1757,7 @@
         <v>COF-02</v>
       </c>
       <c r="B34" t="str">
-        <v>Location banche métallique (travaux)</v>
+        <v>"Location banche métallique (travaux)"</v>
       </c>
       <c r="C34" t="str">
         <v>Coffrage</v>
@@ -1768,17 +1768,17 @@
       <c r="E34" t="str">
         <v>m2</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="str">
         <v>12000</v>
       </c>
       <c r="G34" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H34" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I34" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J34" t="str">
         <v>14/10/2026</v>
@@ -1798,7 +1798,7 @@
         <v>COF-03</v>
       </c>
       <c r="B35" t="str">
-        <v>Étai métallique neuf 5,00 m</v>
+        <v>"Étai métallique neuf 5,00 m"</v>
       </c>
       <c r="C35" t="str">
         <v>Coffrage</v>
@@ -1809,17 +1809,17 @@
       <c r="E35" t="str">
         <v>u</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="str">
         <v>18000</v>
       </c>
       <c r="G35" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H35" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I35" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J35" t="str">
         <v>14/10/2026</v>
@@ -1839,7 +1839,7 @@
         <v>COF-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Étai métallique neuf 4,00 m</v>
+        <v>"Étai métallique neuf 4,00 m"</v>
       </c>
       <c r="C36" t="str">
         <v>Coffrage</v>
@@ -1850,17 +1850,17 @@
       <c r="E36" t="str">
         <v>u</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="str">
         <v>14000</v>
       </c>
       <c r="G36" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H36" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I36" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J36" t="str">
         <v>14/10/2026</v>
@@ -1880,7 +1880,7 @@
         <v>COF-05</v>
       </c>
       <c r="B37" t="str">
-        <v>Étai métallique neuf 3,60 m</v>
+        <v>"Étai métallique neuf 3,60 m"</v>
       </c>
       <c r="C37" t="str">
         <v>Coffrage</v>
@@ -1891,17 +1891,17 @@
       <c r="E37" t="str">
         <v>u</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="str">
         <v>11000</v>
       </c>
       <c r="G37" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H37" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I37" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J37" t="str">
         <v>14/10/2026</v>
@@ -1921,7 +1921,7 @@
         <v>COF-06</v>
       </c>
       <c r="B38" t="str">
-        <v>Location étai métallique d'occasion 4,00 m</v>
+        <v>"Location étai métallique d'occasion 4,00 m"</v>
       </c>
       <c r="C38" t="str">
         <v>Coffrage</v>
@@ -1932,17 +1932,17 @@
       <c r="E38" t="str">
         <v>jour</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="str">
         <v>150</v>
       </c>
       <c r="G38" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H38" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I38" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J38" t="str">
         <v>14/10/2026</v>
@@ -1962,7 +1962,7 @@
         <v>COF-07</v>
       </c>
       <c r="B39" t="str">
-        <v>Location étai métallique d'occasion 3,60 m</v>
+        <v>"Location étai métallique d'occasion 3,60 m"</v>
       </c>
       <c r="C39" t="str">
         <v>Coffrage</v>
@@ -1973,17 +1973,17 @@
       <c r="E39" t="str">
         <v>jour</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="str">
         <v>100</v>
       </c>
       <c r="G39" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H39" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I39" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J39" t="str">
         <v>14/10/2026</v>
@@ -2003,7 +2003,7 @@
         <v>COF-08</v>
       </c>
       <c r="B40" t="str">
-        <v>Étai métallique d'occasion 4,00 m</v>
+        <v>"Étai métallique d'occasion 4,00 m"</v>
       </c>
       <c r="C40" t="str">
         <v>Coffrage</v>
@@ -2014,17 +2014,17 @@
       <c r="E40" t="str">
         <v>u</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="str">
         <v>12000</v>
       </c>
       <c r="G40" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H40" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I40" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J40" t="str">
         <v>14/10/2026</v>
@@ -2044,7 +2044,7 @@
         <v>COF-09</v>
       </c>
       <c r="B41" t="str">
-        <v>Étai métallique d'occasion 3,60 m</v>
+        <v>"Étai métallique d'occasion 3,60 m"</v>
       </c>
       <c r="C41" t="str">
         <v>Coffrage</v>
@@ -2055,17 +2055,17 @@
       <c r="E41" t="str">
         <v>u</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="str">
         <v>8500</v>
       </c>
       <c r="G41" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H41" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I41" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J41" t="str">
         <v>14/10/2026</v>
@@ -2085,7 +2085,7 @@
         <v>COF-10</v>
       </c>
       <c r="B42" t="str">
-        <v>Panneau de coffrage jaune 3000 x 500 x 21 mm</v>
+        <v>"Panneau de coffrage jaune 3000 x 500 x 21 mm"</v>
       </c>
       <c r="C42" t="str">
         <v>Coffrage</v>
@@ -2096,17 +2096,17 @@
       <c r="E42" t="str">
         <v>u</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="str">
         <v>30000</v>
       </c>
       <c r="G42" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H42" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I42" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J42" t="str">
         <v>14/10/2026</v>
@@ -2126,7 +2126,7 @@
         <v>COF-11</v>
       </c>
       <c r="B43" t="str">
-        <v>Panneau de coffrage jaune 3000 x 500 x 27 mm</v>
+        <v>"Panneau de coffrage jaune 3000 x 500 x 27 mm"</v>
       </c>
       <c r="C43" t="str">
         <v>Coffrage</v>
@@ -2137,17 +2137,17 @@
       <c r="E43" t="str">
         <v>u</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="str">
         <v>35000</v>
       </c>
       <c r="G43" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H43" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I43" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J43" t="str">
         <v>14/10/2026</v>
@@ -2167,7 +2167,7 @@
         <v>COF-12</v>
       </c>
       <c r="B44" t="str">
-        <v>Ensemble de cravates pour poteau 15/45 cm</v>
+        <v>"Ensemble de cravates pour poteau 15/45 cm"</v>
       </c>
       <c r="C44" t="str">
         <v>Coffrage</v>
@@ -2178,17 +2178,17 @@
       <c r="E44" t="str">
         <v>u</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="str">
         <v>20000</v>
       </c>
       <c r="G44" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H44" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I44" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J44" t="str">
         <v>14/10/2026</v>
@@ -2208,7 +2208,7 @@
         <v>COF-13</v>
       </c>
       <c r="B45" t="str">
-        <v>Clavette de fixation</v>
+        <v>"Clavette de fixation"</v>
       </c>
       <c r="C45" t="str">
         <v>Coffrage</v>
@@ -2219,17 +2219,17 @@
       <c r="E45" t="str">
         <v>u</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="str">
         <v>800</v>
       </c>
       <c r="G45" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H45" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I45" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J45" t="str">
         <v>14/10/2026</v>
@@ -2249,7 +2249,7 @@
         <v>COF-14</v>
       </c>
       <c r="B46" t="str">
-        <v>Poutrelle H20, longueur 3,90 m</v>
+        <v>"Poutrelle H20, longueur 3,90 m"</v>
       </c>
       <c r="C46" t="str">
         <v>Coffrage</v>
@@ -2260,17 +2260,17 @@
       <c r="E46" t="str">
         <v>ml</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="str">
         <v>8000</v>
       </c>
       <c r="G46" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H46" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I46" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J46" t="str">
         <v>14/10/2026</v>
@@ -2290,7 +2290,7 @@
         <v>COF-15</v>
       </c>
       <c r="B47" t="str">
-        <v>Fourche à 4 voies H20</v>
+        <v>"Fourche à 4 voies H20"</v>
       </c>
       <c r="C47" t="str">
         <v>Coffrage</v>
@@ -2301,17 +2301,17 @@
       <c r="E47" t="str">
         <v>u</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="str">
         <v>7000</v>
       </c>
       <c r="G47" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H47" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I47" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J47" t="str">
         <v>14/10/2026</v>
@@ -2331,7 +2331,7 @@
         <v>COF-16</v>
       </c>
       <c r="B48" t="str">
-        <v>Vérin de réglage peint, neuf</v>
+        <v>"Vérin de réglage peint, neuf"</v>
       </c>
       <c r="C48" t="str">
         <v>Coffrage</v>
@@ -2342,17 +2342,17 @@
       <c r="E48" t="str">
         <v>u</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="str">
         <v>20000</v>
       </c>
       <c r="G48" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H48" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I48" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J48" t="str">
         <v>14/10/2026</v>
@@ -2372,7 +2372,7 @@
         <v>COF-17</v>
       </c>
       <c r="B49" t="str">
-        <v>Vérin de réglage, occasion</v>
+        <v>"Vérin de réglage, occasion"</v>
       </c>
       <c r="C49" t="str">
         <v>Coffrage</v>
@@ -2383,17 +2383,17 @@
       <c r="E49" t="str">
         <v>u</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="str">
         <v>15000</v>
       </c>
       <c r="G49" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H49" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I49" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J49" t="str">
         <v>14/10/2026</v>
@@ -2413,7 +2413,7 @@
         <v>COF-18</v>
       </c>
       <c r="B50" t="str">
-        <v>Trépied d'étai métallique 6 kg</v>
+        <v>"Trépied d'étai métallique 6 kg"</v>
       </c>
       <c r="C50" t="str">
         <v>Coffrage</v>
@@ -2424,17 +2424,17 @@
       <c r="E50" t="str">
         <v>u</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="str">
         <v>15000</v>
       </c>
       <c r="G50" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H50" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I50" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J50" t="str">
         <v>14/10/2026</v>
@@ -2454,7 +2454,7 @@
         <v>COF-19</v>
       </c>
       <c r="B51" t="str">
-        <v>Contreplaqué bakélisé 2440 x 1220 x 1800 mm</v>
+        <v>"Contreplaqué bakélisé 2440 x 1220 x 1800 mm"</v>
       </c>
       <c r="C51" t="str">
         <v>Coffrage</v>
@@ -2465,17 +2465,17 @@
       <c r="E51" t="str">
         <v>u</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="str">
         <v>30000</v>
       </c>
       <c r="G51" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H51" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I51" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J51" t="str">
         <v>14/10/2026</v>
@@ -2495,7 +2495,7 @@
         <v>COF-20</v>
       </c>
       <c r="B52" t="str">
-        <v>Contreplaqué bakélisé 2500 x 1250 x 1800 mm</v>
+        <v>"Contreplaqué bakélisé 2500 x 1250 x 1800 mm"</v>
       </c>
       <c r="C52" t="str">
         <v>Coffrage</v>
@@ -2506,17 +2506,17 @@
       <c r="E52" t="str">
         <v>u</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="str">
         <v>35000</v>
       </c>
       <c r="G52" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H52" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I52" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J52" t="str">
         <v>14/10/2026</v>
@@ -2536,7 +2536,7 @@
         <v>COF-21</v>
       </c>
       <c r="B53" t="str">
-        <v>Contreplaqué bakélisé 2500 x 1250 x 2100 mm</v>
+        <v>"Contreplaqué bakélisé 2500 x 1250 x 2100 mm"</v>
       </c>
       <c r="C53" t="str">
         <v>Coffrage</v>
@@ -2547,17 +2547,17 @@
       <c r="E53" t="str">
         <v>u</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="str">
         <v>50000</v>
       </c>
       <c r="G53" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H53" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I53" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J53" t="str">
         <v>14/10/2026</v>
@@ -2577,7 +2577,7 @@
         <v>COF-22</v>
       </c>
       <c r="B54" t="str">
-        <v>Pince de dalle</v>
+        <v>"Pince de dalle"</v>
       </c>
       <c r="C54" t="str">
         <v>Coffrage</v>
@@ -2588,17 +2588,17 @@
       <c r="E54" t="str">
         <v>u</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="str">
         <v>22500</v>
       </c>
       <c r="G54" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H54" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I54" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J54" t="str">
         <v>14/10/2026</v>
@@ -2618,7 +2618,7 @@
         <v>COF-23</v>
       </c>
       <c r="B55" t="str">
-        <v>Collier galvanisé forgé</v>
+        <v>"Collier galvanisé forgé"</v>
       </c>
       <c r="C55" t="str">
         <v>Coffrage</v>
@@ -2629,17 +2629,17 @@
       <c r="E55" t="str">
         <v>u</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="str">
         <v>2500</v>
       </c>
       <c r="G55" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H55" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I55" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J55" t="str">
         <v>14/10/2026</v>
@@ -2659,7 +2659,7 @@
         <v>COF-24</v>
       </c>
       <c r="B56" t="str">
-        <v>Collier fixe en tôle</v>
+        <v>"Collier fixe en tôle"</v>
       </c>
       <c r="C56" t="str">
         <v>Coffrage</v>
@@ -2670,17 +2670,17 @@
       <c r="E56" t="str">
         <v>u</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="str">
         <v>1750</v>
       </c>
       <c r="G56" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H56" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I56" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J56" t="str">
         <v>14/10/2026</v>
@@ -2700,7 +2700,7 @@
         <v>COF-25</v>
       </c>
       <c r="B57" t="str">
-        <v>Collier mobile en tôle</v>
+        <v>"Collier mobile en tôle"</v>
       </c>
       <c r="C57" t="str">
         <v>Coffrage</v>
@@ -2711,17 +2711,17 @@
       <c r="E57" t="str">
         <v>u</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="str">
         <v>2000</v>
       </c>
       <c r="G57" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H57" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I57" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J57" t="str">
         <v>14/10/2026</v>
@@ -2741,7 +2741,7 @@
         <v>COF-26</v>
       </c>
       <c r="B58" t="str">
-        <v>Tige de coffrage Artéon, neuve</v>
+        <v>"Tige de coffrage Artéon, neuve"</v>
       </c>
       <c r="C58" t="str">
         <v>Coffrage</v>
@@ -2752,17 +2752,17 @@
       <c r="E58" t="str">
         <v>u</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="str">
         <v>4000</v>
       </c>
       <c r="G58" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H58" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I58" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J58" t="str">
         <v>14/10/2026</v>
@@ -2782,7 +2782,7 @@
         <v>COF-27</v>
       </c>
       <c r="B59" t="str">
-        <v>Serre-joint français neuf</v>
+        <v>"Serre-joint français neuf"</v>
       </c>
       <c r="C59" t="str">
         <v>Coffrage</v>
@@ -2793,17 +2793,17 @@
       <c r="E59" t="str">
         <v>u</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="str">
         <v>10000</v>
       </c>
       <c r="G59" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H59" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I59" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J59" t="str">
         <v>14/10/2026</v>
@@ -2823,7 +2823,7 @@
         <v>COF-28</v>
       </c>
       <c r="B60" t="str">
-        <v>Serre-joint français occasion</v>
+        <v>"Serre-joint français occasion"</v>
       </c>
       <c r="C60" t="str">
         <v>Coffrage</v>
@@ -2834,17 +2834,17 @@
       <c r="E60" t="str">
         <v>u</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="str">
         <v>5000</v>
       </c>
       <c r="G60" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H60" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I60" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J60" t="str">
         <v>14/10/2026</v>
@@ -2864,7 +2864,7 @@
         <v>ECH-01</v>
       </c>
       <c r="B61" t="str">
-        <v>Échafaudage léger importé neuf</v>
+        <v>"Échafaudage léger importé neuf"</v>
       </c>
       <c r="C61" t="str">
         <v>Installation de chantier</v>
@@ -2875,17 +2875,17 @@
       <c r="E61" t="str">
         <v>m2</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="str">
         <v>20000</v>
       </c>
       <c r="G61" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H61" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I61" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J61" t="str">
         <v>14/10/2026</v>
@@ -2905,7 +2905,7 @@
         <v>ECH-02</v>
       </c>
       <c r="B62" t="str">
-        <v>Location échafaudage léger importé</v>
+        <v>"Location échafaudage léger importé"</v>
       </c>
       <c r="C62" t="str">
         <v>Installation de chantier</v>
@@ -2916,17 +2916,17 @@
       <c r="E62" t="str">
         <v>m2/jour</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="str">
         <v>1500</v>
       </c>
       <c r="G62" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H62" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I62" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J62" t="str">
         <v>14/10/2026</v>
@@ -2946,7 +2946,7 @@
         <v>TER-01</v>
       </c>
       <c r="B63" t="str">
-        <v>Abattage et dessouchage d'arbre, circonférence 1 à 3 m</v>
+        <v>"Abattage et dessouchage d'arbre, circonférence 1 à 3 m"</v>
       </c>
       <c r="C63" t="str">
         <v>Terrassement</v>
@@ -2957,17 +2957,17 @@
       <c r="E63" t="str">
         <v>u</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="str">
         <v>111743</v>
       </c>
       <c r="G63" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H63" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I63" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J63" t="str">
         <v>14/10/2026</v>
@@ -2987,7 +2987,7 @@
         <v>TER-02</v>
       </c>
       <c r="B64" t="str">
-        <v>Abattage et dessouchage d'arbre, circonférence &gt; 3 m</v>
+        <v>"Abattage et dessouchage d'arbre, circonférence &gt; 3 m"</v>
       </c>
       <c r="C64" t="str">
         <v>Terrassement</v>
@@ -2998,17 +2998,17 @@
       <c r="E64" t="str">
         <v>u</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="str">
         <v>217229</v>
       </c>
       <c r="G64" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H64" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I64" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J64" t="str">
         <v>14/10/2026</v>
@@ -3028,7 +3028,7 @@
         <v>TER-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Décapage à la pioche (terre végétale)</v>
+        <v>"Décapage à la pioche (terre végétale)"</v>
       </c>
       <c r="C65" t="str">
         <v>Terrassement</v>
@@ -3039,17 +3039,17 @@
       <c r="E65" t="str">
         <v>m2</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="str">
         <v>748</v>
       </c>
       <c r="G65" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H65" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I65" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J65" t="str">
         <v>14/10/2026</v>
@@ -3069,7 +3069,7 @@
         <v>TER-04</v>
       </c>
       <c r="B66" t="str">
-        <v>Décapage à la pelle (terre végétale)</v>
+        <v>"Décapage à la pelle (terre végétale)"</v>
       </c>
       <c r="C66" t="str">
         <v>Terrassement</v>
@@ -3080,17 +3080,17 @@
       <c r="E66" t="str">
         <v>m2</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="str">
         <v>467</v>
       </c>
       <c r="G66" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H66" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I66" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J66" t="str">
         <v>14/10/2026</v>
@@ -3110,7 +3110,7 @@
         <v>TER-05</v>
       </c>
       <c r="B67" t="str">
-        <v>Débalis mis en dépôt</v>
+        <v>"Débalis mis en dépôt"</v>
       </c>
       <c r="C67" t="str">
         <v>Terrassement</v>
@@ -3121,17 +3121,17 @@
       <c r="E67" t="str">
         <v>m3</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="str">
         <v>2280</v>
       </c>
       <c r="G67" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H67" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I67" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J67" t="str">
         <v>14/10/2026</v>
@@ -3151,7 +3151,7 @@
         <v>TER-06</v>
       </c>
       <c r="B68" t="str">
-        <v>Évacuation de la terre végétale à la décharge</v>
+        <v>"Évacuation de la terre végétale à la décharge"</v>
       </c>
       <c r="C68" t="str">
         <v>Terrassement</v>
@@ -3162,17 +3162,17 @@
       <c r="E68" t="str">
         <v>m3</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="str">
         <v>653</v>
       </c>
       <c r="G68" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H68" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I68" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J68" t="str">
         <v>14/10/2026</v>
@@ -3192,7 +3192,7 @@
         <v>TER-07</v>
       </c>
       <c r="B69" t="str">
-        <v>Transport à la décharge publique</v>
+        <v>"Transport à la décharge publique"</v>
       </c>
       <c r="C69" t="str">
         <v>Terrassement</v>
@@ -3203,17 +3203,17 @@
       <c r="E69" t="str">
         <v>m3.km</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="str">
         <v>218</v>
       </c>
       <c r="G69" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H69" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I69" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J69" t="str">
         <v>14/10/2026</v>
@@ -3233,7 +3233,7 @@
         <v>TER-08</v>
       </c>
       <c r="B70" t="str">
-        <v>Fouilles mécaniques en excavation, 1re catégorie</v>
+        <v>"Fouilles mécaniques en excavation, 1re catégorie"</v>
       </c>
       <c r="C70" t="str">
         <v>Terrassement</v>
@@ -3244,17 +3244,17 @@
       <c r="E70" t="str">
         <v>m3</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="str">
         <v>1392</v>
       </c>
       <c r="G70" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H70" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I70" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J70" t="str">
         <v>14/10/2026</v>
@@ -3274,7 +3274,7 @@
         <v>TER-09</v>
       </c>
       <c r="B71" t="str">
-        <v>Fouilles mécaniques en excavation, 2e catégorie</v>
+        <v>"Fouilles mécaniques en excavation, 2e catégorie"</v>
       </c>
       <c r="C71" t="str">
         <v>Terrassement</v>
@@ -3285,17 +3285,17 @@
       <c r="E71" t="str">
         <v>m3</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="str">
         <v>1537</v>
       </c>
       <c r="G71" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H71" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I71" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J71" t="str">
         <v>14/10/2026</v>
@@ -3315,7 +3315,7 @@
         <v>TER-10</v>
       </c>
       <c r="B72" t="str">
-        <v>Fouilles mécaniques en excavation, 3e catégorie</v>
+        <v>"Fouilles mécaniques en excavation, 3e catégorie"</v>
       </c>
       <c r="C72" t="str">
         <v>Terrassement</v>
@@ -3326,17 +3326,17 @@
       <c r="E72" t="str">
         <v>m3</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="str">
         <v>1687</v>
       </c>
       <c r="G72" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H72" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I72" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J72" t="str">
         <v>14/10/2026</v>
@@ -3356,7 +3356,7 @@
         <v>TER-11</v>
       </c>
       <c r="B73" t="str">
-        <v>Fouilles mécaniques en excavation, 4e catégorie</v>
+        <v>"Fouilles mécaniques en excavation, 4e catégorie"</v>
       </c>
       <c r="C73" t="str">
         <v>Terrassement</v>
@@ -3367,17 +3367,17 @@
       <c r="E73" t="str">
         <v>m3</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="str">
         <v>1905</v>
       </c>
       <c r="G73" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H73" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I73" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J73" t="str">
         <v>14/10/2026</v>
@@ -3397,7 +3397,7 @@
         <v>TER-12</v>
       </c>
       <c r="B74" t="str">
-        <v>Fouilles mécaniques en puits, 1re catégorie</v>
+        <v>"Fouilles mécaniques en puits, 1re catégorie"</v>
       </c>
       <c r="C74" t="str">
         <v>Terrassement</v>
@@ -3408,17 +3408,17 @@
       <c r="E74" t="str">
         <v>m3</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="str">
         <v>2738</v>
       </c>
       <c r="G74" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H74" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I74" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J74" t="str">
         <v>14/10/2026</v>
@@ -3438,7 +3438,7 @@
         <v>TER-13</v>
       </c>
       <c r="B75" t="str">
-        <v>Fouilles mécaniques en puits, 2e catégorie</v>
+        <v>"Fouilles mécaniques en puits, 2e catégorie"</v>
       </c>
       <c r="C75" t="str">
         <v>Terrassement</v>
@@ -3449,17 +3449,17 @@
       <c r="E75" t="str">
         <v>m3</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="str">
         <v>2987</v>
       </c>
       <c r="G75" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H75" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I75" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J75" t="str">
         <v>14/10/2026</v>
@@ -3479,7 +3479,7 @@
         <v>TER-14</v>
       </c>
       <c r="B76" t="str">
-        <v>Fouilles mécaniques en puits, 3e catégorie</v>
+        <v>"Fouilles mécaniques en puits, 3e catégorie"</v>
       </c>
       <c r="C76" t="str">
         <v>Terrassement</v>
@@ -3490,17 +3490,17 @@
       <c r="E76" t="str">
         <v>m3</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="str">
         <v>3356</v>
       </c>
       <c r="G76" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H76" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I76" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J76" t="str">
         <v>14/10/2026</v>
@@ -3520,7 +3520,7 @@
         <v>TER-15</v>
       </c>
       <c r="B77" t="str">
-        <v>Fouilles mécaniques en puits, 4e catégorie</v>
+        <v>"Fouilles mécaniques en puits, 4e catégorie"</v>
       </c>
       <c r="C77" t="str">
         <v>Terrassement</v>
@@ -3531,17 +3531,17 @@
       <c r="E77" t="str">
         <v>m3</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="str">
         <v>3850</v>
       </c>
       <c r="G77" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H77" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I77" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J77" t="str">
         <v>14/10/2026</v>
@@ -3561,7 +3561,7 @@
         <v>TER-16</v>
       </c>
       <c r="B78" t="str">
-        <v>Fouilles mécaniques en tranchée, 1re catégorie</v>
+        <v>"Fouilles mécaniques en tranchée, 1re catégorie"</v>
       </c>
       <c r="C78" t="str">
         <v>Terrassement</v>
@@ -3572,17 +3572,17 @@
       <c r="E78" t="str">
         <v>m3</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="str">
         <v>977</v>
       </c>
       <c r="G78" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H78" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I78" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J78" t="str">
         <v>14/10/2026</v>
@@ -3602,7 +3602,7 @@
         <v>TER-17</v>
       </c>
       <c r="B79" t="str">
-        <v>Fouilles mécaniques en tranchée, 2e catégorie</v>
+        <v>"Fouilles mécaniques en tranchée, 2e catégorie"</v>
       </c>
       <c r="C79" t="str">
         <v>Terrassement</v>
@@ -3613,17 +3613,17 @@
       <c r="E79" t="str">
         <v>m3</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="str">
         <v>1189</v>
       </c>
       <c r="G79" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H79" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I79" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J79" t="str">
         <v>14/10/2026</v>
@@ -3643,7 +3643,7 @@
         <v>TER-18</v>
       </c>
       <c r="B80" t="str">
-        <v>Fouilles mécaniques en tranchée, 3e catégorie</v>
+        <v>"Fouilles mécaniques en tranchée, 3e catégorie"</v>
       </c>
       <c r="C80" t="str">
         <v>Terrassement</v>
@@ -3654,17 +3654,17 @@
       <c r="E80" t="str">
         <v>m3</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="str">
         <v>1586</v>
       </c>
       <c r="G80" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H80" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I80" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J80" t="str">
         <v>14/10/2026</v>
@@ -3684,7 +3684,7 @@
         <v>TER-19</v>
       </c>
       <c r="B81" t="str">
-        <v>Fouilles mécaniques en tranchée, 4e catégorie</v>
+        <v>"Fouilles mécaniques en tranchée, 4e catégorie"</v>
       </c>
       <c r="C81" t="str">
         <v>Terrassement</v>
@@ -3695,17 +3695,17 @@
       <c r="E81" t="str">
         <v>m3</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="str">
         <v>2281</v>
       </c>
       <c r="G81" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H81" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I81" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J81" t="str">
         <v>14/10/2026</v>
@@ -3725,7 +3725,7 @@
         <v>TER-20</v>
       </c>
       <c r="B82" t="str">
-        <v>Fouilles manuelles en excavation, 1re catégorie</v>
+        <v>"Fouilles manuelles en excavation, 1re catégorie"</v>
       </c>
       <c r="C82" t="str">
         <v>Terrassement</v>
@@ -3736,17 +3736,17 @@
       <c r="E82" t="str">
         <v>m3</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="str">
         <v>2466</v>
       </c>
       <c r="G82" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H82" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I82" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J82" t="str">
         <v>14/10/2026</v>
@@ -3766,7 +3766,7 @@
         <v>TER-21</v>
       </c>
       <c r="B83" t="str">
-        <v>Fouilles manuelles en excavation, 2e catégorie</v>
+        <v>"Fouilles manuelles en excavation, 2e catégorie"</v>
       </c>
       <c r="C83" t="str">
         <v>Terrassement</v>
@@ -3777,17 +3777,17 @@
       <c r="E83" t="str">
         <v>m3</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="str">
         <v>2868</v>
       </c>
       <c r="G83" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H83" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I83" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J83" t="str">
         <v>14/10/2026</v>
@@ -3807,7 +3807,7 @@
         <v>TER-22</v>
       </c>
       <c r="B84" t="str">
-        <v>Fouilles manuelles en excavation, 3e catégorie</v>
+        <v>"Fouilles manuelles en excavation, 3e catégorie"</v>
       </c>
       <c r="C84" t="str">
         <v>Terrassement</v>
@@ -3818,17 +3818,17 @@
       <c r="E84" t="str">
         <v>m3</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="str">
         <v>3212</v>
       </c>
       <c r="G84" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H84" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I84" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J84" t="str">
         <v>14/10/2026</v>
@@ -3840,7 +3840,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M84" t="str">
-        <v>Lecture incertaine du PDF</v>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -3848,7 +3848,7 @@
         <v>TER-23</v>
       </c>
       <c r="B85" t="str">
-        <v>Fouilles manuelles en excavation, 4e catégorie</v>
+        <v>"Fouilles manuelles en excavation, 4e catégorie"</v>
       </c>
       <c r="C85" t="str">
         <v>Terrassement</v>
@@ -3859,17 +3859,17 @@
       <c r="E85" t="str">
         <v>m3</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="str">
         <v>8604</v>
       </c>
       <c r="G85" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H85" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I85" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J85" t="str">
         <v>14/10/2026</v>
@@ -3889,7 +3889,7 @@
         <v>TER-24</v>
       </c>
       <c r="B86" t="str">
-        <v>Fouilles manuelles en puits, 1re catégorie</v>
+        <v>"Fouilles manuelles en puits, 1re catégorie"</v>
       </c>
       <c r="C86" t="str">
         <v>Terrassement</v>
@@ -3900,17 +3900,17 @@
       <c r="E86" t="str">
         <v>m3</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="str">
         <v>2849</v>
       </c>
       <c r="G86" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H86" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I86" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J86" t="str">
         <v>14/10/2026</v>
@@ -3930,7 +3930,7 @@
         <v>TER-25</v>
       </c>
       <c r="B87" t="str">
-        <v>Fouilles manuelles en puits, 2e catégorie</v>
+        <v>"Fouilles manuelles en puits, 2e catégorie"</v>
       </c>
       <c r="C87" t="str">
         <v>Terrassement</v>
@@ -3941,17 +3941,17 @@
       <c r="E87" t="str">
         <v>m3</v>
       </c>
-      <c r="F87">
+      <c r="F87" t="str">
         <v>3275</v>
       </c>
       <c r="G87" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H87" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I87" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J87" t="str">
         <v>14/10/2026</v>
@@ -3971,7 +3971,7 @@
         <v>TER-26</v>
       </c>
       <c r="B88" t="str">
-        <v>Fouilles manuelles en puits, 3e catégorie</v>
+        <v>"Fouilles manuelles en puits, 3e catégorie"</v>
       </c>
       <c r="C88" t="str">
         <v>Terrassement</v>
@@ -3982,17 +3982,17 @@
       <c r="E88" t="str">
         <v>m3</v>
       </c>
-      <c r="F88">
+      <c r="F88" t="str">
         <v>3822</v>
       </c>
       <c r="G88" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H88" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I88" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J88" t="str">
         <v>14/10/2026</v>
@@ -4012,7 +4012,7 @@
         <v>TER-27</v>
       </c>
       <c r="B89" t="str">
-        <v>Fouilles manuelles en puits, 4e catégorie</v>
+        <v>"Fouilles manuelles en puits, 4e catégorie"</v>
       </c>
       <c r="C89" t="str">
         <v>Terrassement</v>
@@ -4023,17 +4023,17 @@
       <c r="E89" t="str">
         <v>m3</v>
       </c>
-      <c r="F89">
+      <c r="F89" t="str">
         <v>10116</v>
       </c>
       <c r="G89" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H89" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I89" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J89" t="str">
         <v>14/10/2026</v>
@@ -4053,7 +4053,7 @@
         <v>TER-28</v>
       </c>
       <c r="B90" t="str">
-        <v>Fouilles manuelles en tranchée, 1re catégorie</v>
+        <v>"Fouilles manuelles en tranchée, 1re catégorie"</v>
       </c>
       <c r="C90" t="str">
         <v>Terrassement</v>
@@ -4064,17 +4064,17 @@
       <c r="E90" t="str">
         <v>m3</v>
       </c>
-      <c r="F90">
+      <c r="F90" t="str">
         <v>2744</v>
       </c>
       <c r="G90" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H90" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I90" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J90" t="str">
         <v>14/10/2026</v>
@@ -4094,7 +4094,7 @@
         <v>TER-29</v>
       </c>
       <c r="B91" t="str">
-        <v>Fouilles manuelles en tranchée, 2e catégorie</v>
+        <v>"Fouilles manuelles en tranchée, 2e catégorie"</v>
       </c>
       <c r="C91" t="str">
         <v>Terrassement</v>
@@ -4105,17 +4105,17 @@
       <c r="E91" t="str">
         <v>m3</v>
       </c>
-      <c r="F91">
+      <c r="F91" t="str">
         <v>3143</v>
       </c>
       <c r="G91" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H91" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I91" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J91" t="str">
         <v>14/10/2026</v>
@@ -4135,7 +4135,7 @@
         <v>TER-30</v>
       </c>
       <c r="B92" t="str">
-        <v>Fouilles manuelles en tranchée, 3e catégorie</v>
+        <v>"Fouilles manuelles en tranchée, 3e catégorie"</v>
       </c>
       <c r="C92" t="str">
         <v>Terrassement</v>
@@ -4146,17 +4146,17 @@
       <c r="E92" t="str">
         <v>m3</v>
       </c>
-      <c r="F92">
+      <c r="F92" t="str">
         <v>3656</v>
       </c>
       <c r="G92" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H92" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I92" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J92" t="str">
         <v>14/10/2026</v>
@@ -4176,7 +4176,7 @@
         <v>TER-31</v>
       </c>
       <c r="B93" t="str">
-        <v>Fouilles manuelles en tranchée, 4e catégorie</v>
+        <v>"Fouilles manuelles en tranchée, 4e catégorie"</v>
       </c>
       <c r="C93" t="str">
         <v>Terrassement</v>
@@ -4187,17 +4187,17 @@
       <c r="E93" t="str">
         <v>m3</v>
       </c>
-      <c r="F93">
+      <c r="F93" t="str">
         <v>9747</v>
       </c>
       <c r="G93" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H93" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I93" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J93" t="str">
         <v>14/10/2026</v>
@@ -4217,7 +4217,7 @@
         <v>REM-01</v>
       </c>
       <c r="B94" t="str">
-        <v>Remblai de terre, épaisseur 15 cm</v>
+        <v>"Remblai de terre, épaisseur 15 cm"</v>
       </c>
       <c r="C94" t="str">
         <v>Remblai</v>
@@ -4228,17 +4228,17 @@
       <c r="E94" t="str">
         <v>m3</v>
       </c>
-      <c r="F94">
+      <c r="F94" t="str">
         <v>4947</v>
       </c>
       <c r="G94" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H94" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I94" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J94" t="str">
         <v>14/10/2026</v>
@@ -4258,7 +4258,7 @@
         <v>REM-02</v>
       </c>
       <c r="B95" t="str">
-        <v>Apport de terre graveleuse</v>
+        <v>"Apport de terre graveleuse"</v>
       </c>
       <c r="C95" t="str">
         <v>Remblai</v>
@@ -4269,17 +4269,17 @@
       <c r="E95" t="str">
         <v>m3</v>
       </c>
-      <c r="F95">
+      <c r="F95" t="str">
         <v>4617</v>
       </c>
       <c r="G95" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H95" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I95" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J95" t="str">
         <v>14/10/2026</v>
@@ -4299,7 +4299,7 @@
         <v>REM-03</v>
       </c>
       <c r="B96" t="str">
-        <v>Apport de terre argilo-sableuse</v>
+        <v>"Apport de terre argilo-sableuse"</v>
       </c>
       <c r="C96" t="str">
         <v>Remblai</v>
@@ -4310,17 +4310,17 @@
       <c r="E96" t="str">
         <v>m3</v>
       </c>
-      <c r="F96">
+      <c r="F96" t="str">
         <v>862</v>
       </c>
       <c r="G96" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H96" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I96" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J96" t="str">
         <v>14/10/2026</v>
@@ -4332,7 +4332,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M96" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -4340,7 +4340,7 @@
         <v>REM-04</v>
       </c>
       <c r="B97" t="str">
-        <v>Remblai manuel des fouilles</v>
+        <v>"Remblai manuel des fouilles"</v>
       </c>
       <c r="C97" t="str">
         <v>Remblai</v>
@@ -4351,17 +4351,17 @@
       <c r="E97" t="str">
         <v>m3</v>
       </c>
-      <c r="F97">
+      <c r="F97" t="str">
         <v>1121</v>
       </c>
       <c r="G97" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H97" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I97" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J97" t="str">
         <v>14/10/2026</v>
@@ -4373,7 +4373,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M97" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -4381,7 +4381,7 @@
         <v>REM-05</v>
       </c>
       <c r="B98" t="str">
-        <v>Remblai compacté sous dallage</v>
+        <v>"Remblai compacté sous dallage"</v>
       </c>
       <c r="C98" t="str">
         <v>Remblai</v>
@@ -4392,17 +4392,17 @@
       <c r="E98" t="str">
         <v>m3</v>
       </c>
-      <c r="F98">
+      <c r="F98" t="str">
         <v>2789</v>
       </c>
       <c r="G98" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H98" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I98" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J98" t="str">
         <v>14/10/2026</v>
@@ -4414,7 +4414,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M98" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -4422,7 +4422,7 @@
         <v>REM-06</v>
       </c>
       <c r="B99" t="str">
-        <v>Épandage des terres</v>
+        <v>"Épandage des terres"</v>
       </c>
       <c r="C99" t="str">
         <v>Remblai</v>
@@ -4433,17 +4433,17 @@
       <c r="E99" t="str">
         <v>m3</v>
       </c>
-      <c r="F99">
+      <c r="F99" t="str">
         <v>774</v>
       </c>
       <c r="G99" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H99" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I99" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J99" t="str">
         <v>14/10/2026</v>
@@ -4455,7 +4455,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M99" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -4463,7 +4463,7 @@
         <v>REM-07</v>
       </c>
       <c r="B100" t="str">
-        <v>Nivellement définitif sous dallage</v>
+        <v>"Nivellement définitif sous dallage"</v>
       </c>
       <c r="C100" t="str">
         <v>Remblai</v>
@@ -4474,17 +4474,17 @@
       <c r="E100" t="str">
         <v>m2</v>
       </c>
-      <c r="F100">
+      <c r="F100" t="str">
         <v>740</v>
       </c>
       <c r="G100" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H100" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I100" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J100" t="str">
         <v>14/10/2026</v>
@@ -4504,7 +4504,7 @@
         <v>REM-08</v>
       </c>
       <c r="B101" t="str">
-        <v>Exécution de talus droit</v>
+        <v>"Exécution de talus droit"</v>
       </c>
       <c r="C101" t="str">
         <v>Remblai</v>
@@ -4515,17 +4515,17 @@
       <c r="E101" t="str">
         <v>m</v>
       </c>
-      <c r="F101">
+      <c r="F101" t="str">
         <v>1052</v>
       </c>
       <c r="G101" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H101" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I101" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J101" t="str">
         <v>14/10/2026</v>
@@ -4537,7 +4537,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M101" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -4545,7 +4545,7 @@
         <v>REM-09</v>
       </c>
       <c r="B102" t="str">
-        <v>Exécution de talus courbe</v>
+        <v>"Exécution de talus courbe"</v>
       </c>
       <c r="C102" t="str">
         <v>Remblai</v>
@@ -4556,17 +4556,17 @@
       <c r="E102" t="str">
         <v>m3</v>
       </c>
-      <c r="F102">
+      <c r="F102" t="str">
         <v>3025</v>
       </c>
       <c r="G102" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H102" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I102" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J102" t="str">
         <v>14/10/2026</v>
@@ -4586,7 +4586,7 @@
         <v>REM-10</v>
       </c>
       <c r="B103" t="str">
-        <v>Évacuation des déblais excédentaires</v>
+        <v>"Évacuation des déblais excédentaires"</v>
       </c>
       <c r="C103" t="str">
         <v>Remblai</v>
@@ -4597,17 +4597,17 @@
       <c r="E103" t="str">
         <v>m</v>
       </c>
-      <c r="F103">
+      <c r="F103" t="str">
         <v>680</v>
       </c>
       <c r="G103" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H103" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I103" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J103" t="str">
         <v>14/10/2026</v>
@@ -4619,7 +4619,7 @@
         <v>à vérifier</v>
       </c>
       <c r="M103" t="str">
-        <v>Unité à confirmer dans le PDF</v>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -4627,7 +4627,7 @@
         <v>BET-01</v>
       </c>
       <c r="B104" t="str">
-        <v>Béton de propreté C16/20 (BPE)</v>
+        <v>"Béton de propreté C16/20 (BPE)"</v>
       </c>
       <c r="C104" t="str">
         <v>Béton</v>
@@ -4638,17 +4638,17 @@
       <c r="E104" t="str">
         <v>m3</v>
       </c>
-      <c r="F104">
+      <c r="F104" t="str">
         <v>89261</v>
       </c>
       <c r="G104" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H104" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I104" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J104" t="str">
         <v>14/10/2026</v>
@@ -4668,7 +4668,7 @@
         <v>BET-02</v>
       </c>
       <c r="B105" t="str">
-        <v>Béton C30/37 en fondation, radier (BPE)</v>
+        <v>"Béton C30/37 en fondation, radier (BPE)"</v>
       </c>
       <c r="C105" t="str">
         <v>Béton</v>
@@ -4679,17 +4679,17 @@
       <c r="E105" t="str">
         <v>m3</v>
       </c>
-      <c r="F105">
+      <c r="F105" t="str">
         <v>108104</v>
       </c>
       <c r="G105" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H105" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I105" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J105" t="str">
         <v>14/10/2026</v>
@@ -4709,7 +4709,7 @@
         <v>BET-03</v>
       </c>
       <c r="B106" t="str">
-        <v>Béton C30/37 en infrastructure, amorces de poteaux (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, amorces de poteaux (BPE)"</v>
       </c>
       <c r="C106" t="str">
         <v>Béton</v>
@@ -4720,17 +4720,17 @@
       <c r="E106" t="str">
         <v>m3</v>
       </c>
-      <c r="F106">
+      <c r="F106" t="str">
         <v>108975</v>
       </c>
       <c r="G106" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H106" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I106" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J106" t="str">
         <v>14/10/2026</v>
@@ -4750,7 +4750,7 @@
         <v>BET-04</v>
       </c>
       <c r="B107" t="str">
-        <v>Béton C30/37 en infrastructure, voiles banchés (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, voiles banchés (BPE)"</v>
       </c>
       <c r="C107" t="str">
         <v>Béton</v>
@@ -4761,17 +4761,17 @@
       <c r="E107" t="str">
         <v>m3</v>
       </c>
-      <c r="F107">
+      <c r="F107" t="str">
         <v>108265</v>
       </c>
       <c r="G107" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H107" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I107" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J107" t="str">
         <v>14/10/2026</v>
@@ -4791,7 +4791,7 @@
         <v>BET-05</v>
       </c>
       <c r="B108" t="str">
-        <v>Béton C30/37 en infrastructure, poteaux et raidisseurs (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, poteaux et raidisseurs (BPE)"</v>
       </c>
       <c r="C108" t="str">
         <v>Béton</v>
@@ -4802,17 +4802,17 @@
       <c r="E108" t="str">
         <v>m3</v>
       </c>
-      <c r="F108">
+      <c r="F108" t="str">
         <v>108824</v>
       </c>
       <c r="G108" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H108" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I108" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J108" t="str">
         <v>14/10/2026</v>
@@ -4832,7 +4832,7 @@
         <v>BET-06</v>
       </c>
       <c r="B109" t="str">
-        <v>Béton C30/37 en infrastructure, poutres chaînages linteaux (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, poutres chaînages linteaux (BPE)"</v>
       </c>
       <c r="C109" t="str">
         <v>Béton</v>
@@ -4843,17 +4843,17 @@
       <c r="E109" t="str">
         <v>m3</v>
       </c>
-      <c r="F109">
+      <c r="F109" t="str">
         <v>110644</v>
       </c>
       <c r="G109" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H109" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I109" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J109" t="str">
         <v>14/10/2026</v>
@@ -4873,7 +4873,7 @@
         <v>BET-07</v>
       </c>
       <c r="B110" t="str">
-        <v>Béton C30/37 en infrastructure, dalle pleine (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, dalle pleine (BPE)"</v>
       </c>
       <c r="C110" t="str">
         <v>Béton</v>
@@ -4884,17 +4884,17 @@
       <c r="E110" t="str">
         <v>m3</v>
       </c>
-      <c r="F110">
+      <c r="F110" t="str">
         <v>107562</v>
       </c>
       <c r="G110" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H110" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I110" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J110" t="str">
         <v>14/10/2026</v>
@@ -4914,7 +4914,7 @@
         <v>BET-08</v>
       </c>
       <c r="B111" t="str">
-        <v>Béton C30/37 en infrastructure, escaliers (BPE)</v>
+        <v>"Béton C30/37 en infrastructure, escaliers (BPE)"</v>
       </c>
       <c r="C111" t="str">
         <v>Béton</v>
@@ -4925,17 +4925,17 @@
       <c r="E111" t="str">
         <v>m3</v>
       </c>
-      <c r="F111">
+      <c r="F111" t="str">
         <v>108088</v>
       </c>
       <c r="G111" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H111" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I111" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J111" t="str">
         <v>14/10/2026</v>
@@ -4955,7 +4955,7 @@
         <v>BET-09</v>
       </c>
       <c r="B112" t="str">
-        <v>Béton C30/37 en élévation, poteaux (BPE)</v>
+        <v>"Béton C30/37 en élévation, poteaux (BPE)"</v>
       </c>
       <c r="C112" t="str">
         <v>Béton</v>
@@ -4966,17 +4966,17 @@
       <c r="E112" t="str">
         <v>m3</v>
       </c>
-      <c r="F112">
+      <c r="F112" t="str">
         <v>108824</v>
       </c>
       <c r="G112" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H112" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I112" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J112" t="str">
         <v>14/10/2026</v>
@@ -4996,7 +4996,7 @@
         <v>BET-10</v>
       </c>
       <c r="B113" t="str">
-        <v>Béton C30/37 en élévation, poutres chaînages linteaux (BPE)</v>
+        <v>"Béton C30/37 en élévation, poutres chaînages linteaux (BPE)"</v>
       </c>
       <c r="C113" t="str">
         <v>Béton</v>
@@ -5007,17 +5007,17 @@
       <c r="E113" t="str">
         <v>m3</v>
       </c>
-      <c r="F113">
+      <c r="F113" t="str">
         <v>110644</v>
       </c>
       <c r="G113" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H113" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I113" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J113" t="str">
         <v>14/10/2026</v>
@@ -5037,7 +5037,7 @@
         <v>BET-11</v>
       </c>
       <c r="B114" t="str">
-        <v>Béton C30/37 en élévation, dalle pleine (BPE)</v>
+        <v>"Béton C30/37 en élévation, dalle pleine (BPE)"</v>
       </c>
       <c r="C114" t="str">
         <v>Béton</v>
@@ -5048,17 +5048,17 @@
       <c r="E114" t="str">
         <v>m3</v>
       </c>
-      <c r="F114">
+      <c r="F114" t="str">
         <v>107562</v>
       </c>
       <c r="G114" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H114" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I114" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J114" t="str">
         <v>14/10/2026</v>
@@ -5078,7 +5078,7 @@
         <v>BET-12</v>
       </c>
       <c r="B115" t="str">
-        <v>Béton C30/37 en élévation, escaliers (BPE)</v>
+        <v>"Béton C30/37 en élévation, escaliers (BPE)"</v>
       </c>
       <c r="C115" t="str">
         <v>Béton</v>
@@ -5089,17 +5089,17 @@
       <c r="E115" t="str">
         <v>m3</v>
       </c>
-      <c r="F115">
+      <c r="F115" t="str">
         <v>108088</v>
       </c>
       <c r="G115" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H115" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I115" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J115" t="str">
         <v>14/10/2026</v>
@@ -5119,7 +5119,7 @@
         <v>BET-13</v>
       </c>
       <c r="B116" t="str">
-        <v>Béton C30/37 en élévation, voiles (BPE)</v>
+        <v>"Béton C30/37 en élévation, voiles (BPE)"</v>
       </c>
       <c r="C116" t="str">
         <v>Béton</v>
@@ -5130,17 +5130,17 @@
       <c r="E116" t="str">
         <v>m3</v>
       </c>
-      <c r="F116">
+      <c r="F116" t="str">
         <v>108265</v>
       </c>
       <c r="G116" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H116" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I116" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J116" t="str">
         <v>14/10/2026</v>
@@ -5160,7 +5160,7 @@
         <v>BET-150CPA</v>
       </c>
       <c r="B117" t="str">
-        <v>Béton fabriqué chantier dosé 150 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 150 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C117" t="str">
         <v>Béton</v>
@@ -5171,17 +5171,17 @@
       <c r="E117" t="str">
         <v>m3</v>
       </c>
-      <c r="F117">
+      <c r="F117" t="str">
         <v>63972</v>
       </c>
       <c r="G117" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H117" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I117" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J117" t="str">
         <v>14/10/2026</v>
@@ -5201,7 +5201,7 @@
         <v>BET-200CPA</v>
       </c>
       <c r="B118" t="str">
-        <v>Béton fabriqué chantier dosé 200 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 200 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C118" t="str">
         <v>Béton</v>
@@ -5212,17 +5212,17 @@
       <c r="E118" t="str">
         <v>m3</v>
       </c>
-      <c r="F118">
+      <c r="F118" t="str">
         <v>71606</v>
       </c>
       <c r="G118" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H118" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I118" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J118" t="str">
         <v>14/10/2026</v>
@@ -5242,7 +5242,7 @@
         <v>BET-250CPA</v>
       </c>
       <c r="B119" t="str">
-        <v>Béton fabriqué chantier dosé 250 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 250 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C119" t="str">
         <v>Béton</v>
@@ -5253,17 +5253,17 @@
       <c r="E119" t="str">
         <v>m3</v>
       </c>
-      <c r="F119">
+      <c r="F119" t="str">
         <v>79194</v>
       </c>
       <c r="G119" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H119" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I119" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J119" t="str">
         <v>14/10/2026</v>
@@ -5283,7 +5283,7 @@
         <v>BET-300CPA</v>
       </c>
       <c r="B120" t="str">
-        <v>Béton fabriqué chantier dosé 300 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 300 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C120" t="str">
         <v>Béton</v>
@@ -5294,17 +5294,17 @@
       <c r="E120" t="str">
         <v>m3</v>
       </c>
-      <c r="F120">
+      <c r="F120" t="str">
         <v>86782</v>
       </c>
       <c r="G120" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H120" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I120" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J120" t="str">
         <v>14/10/2026</v>
@@ -5324,7 +5324,7 @@
         <v>BET-350CPA</v>
       </c>
       <c r="B121" t="str">
-        <v>Béton fabriqué chantier dosé 350 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 350 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C121" t="str">
         <v>Béton</v>
@@ -5335,17 +5335,17 @@
       <c r="E121" t="str">
         <v>m3</v>
       </c>
-      <c r="F121">
+      <c r="F121" t="str">
         <v>94369</v>
       </c>
       <c r="G121" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H121" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I121" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J121" t="str">
         <v>14/10/2026</v>
@@ -5365,7 +5365,7 @@
         <v>BET-400CPA</v>
       </c>
       <c r="B122" t="str">
-        <v>Béton fabriqué chantier dosé 400 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 400 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C122" t="str">
         <v>Béton</v>
@@ -5376,17 +5376,17 @@
       <c r="E122" t="str">
         <v>m3</v>
       </c>
-      <c r="F122">
+      <c r="F122" t="str">
         <v>101958</v>
       </c>
       <c r="G122" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H122" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I122" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J122" t="str">
         <v>14/10/2026</v>
@@ -5406,7 +5406,7 @@
         <v>BET-450CPA</v>
       </c>
       <c r="B123" t="str">
-        <v>Béton fabriqué chantier dosé 450 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 450 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C123" t="str">
         <v>Béton</v>
@@ -5417,17 +5417,17 @@
       <c r="E123" t="str">
         <v>m3</v>
       </c>
-      <c r="F123">
+      <c r="F123" t="str">
         <v>109545</v>
       </c>
       <c r="G123" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H123" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I123" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J123" t="str">
         <v>14/10/2026</v>
@@ -5447,7 +5447,7 @@
         <v>BET-500CPA</v>
       </c>
       <c r="B124" t="str">
-        <v>Béton fabriqué chantier dosé 500 kg/m3, CPA 42,5 (semelle ou propreté)</v>
+        <v>"Béton fabriqué chantier dosé 500 kg/m3, CPA 42,5 (semelle ou propreté)"</v>
       </c>
       <c r="C124" t="str">
         <v>Béton</v>
@@ -5458,17 +5458,17 @@
       <c r="E124" t="str">
         <v>m3</v>
       </c>
-      <c r="F124">
+      <c r="F124" t="str">
         <v>117133</v>
       </c>
       <c r="G124" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H124" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I124" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J124" t="str">
         <v>14/10/2026</v>
@@ -5488,7 +5488,7 @@
         <v>BET-150CPJ</v>
       </c>
       <c r="B125" t="str">
-        <v>Béton fabriqué chantier dosé 150 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 150 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C125" t="str">
         <v>Béton</v>
@@ -5499,17 +5499,17 @@
       <c r="E125" t="str">
         <v>m3</v>
       </c>
-      <c r="F125">
+      <c r="F125" t="str">
         <v>60804</v>
       </c>
       <c r="G125" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H125" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I125" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J125" t="str">
         <v>14/10/2026</v>
@@ -5529,7 +5529,7 @@
         <v>BET-200CPJ</v>
       </c>
       <c r="B126" t="str">
-        <v>Béton fabriqué chantier dosé 200 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 200 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C126" t="str">
         <v>Béton</v>
@@ -5540,17 +5540,17 @@
       <c r="E126" t="str">
         <v>m3</v>
       </c>
-      <c r="F126">
+      <c r="F126" t="str">
         <v>67382</v>
       </c>
       <c r="G126" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H126" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I126" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J126" t="str">
         <v>14/10/2026</v>
@@ -5570,7 +5570,7 @@
         <v>BET-250CPJ</v>
       </c>
       <c r="B127" t="str">
-        <v>Béton fabriqué chantier dosé 250 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 250 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C127" t="str">
         <v>Béton</v>
@@ -5581,17 +5581,17 @@
       <c r="E127" t="str">
         <v>m3</v>
       </c>
-      <c r="F127">
+      <c r="F127" t="str">
         <v>73914</v>
       </c>
       <c r="G127" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H127" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I127" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J127" t="str">
         <v>14/10/2026</v>
@@ -5611,7 +5611,7 @@
         <v>BET-300CPJ</v>
       </c>
       <c r="B128" t="str">
-        <v>Béton fabriqué chantier dosé 300 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 300 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C128" t="str">
         <v>Béton</v>
@@ -5622,17 +5622,17 @@
       <c r="E128" t="str">
         <v>m3</v>
       </c>
-      <c r="F128">
+      <c r="F128" t="str">
         <v>80445</v>
       </c>
       <c r="G128" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H128" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I128" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J128" t="str">
         <v>14/10/2026</v>
@@ -5652,7 +5652,7 @@
         <v>BET-350CPJ</v>
       </c>
       <c r="B129" t="str">
-        <v>Béton fabriqué chantier dosé 350 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 350 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C129" t="str">
         <v>Béton</v>
@@ -5663,17 +5663,17 @@
       <c r="E129" t="str">
         <v>m3</v>
       </c>
-      <c r="F129">
+      <c r="F129" t="str">
         <v>86977</v>
       </c>
       <c r="G129" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H129" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I129" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J129" t="str">
         <v>14/10/2026</v>
@@ -5693,7 +5693,7 @@
         <v>BET-400CPJ</v>
       </c>
       <c r="B130" t="str">
-        <v>Béton fabriqué chantier dosé 400 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 400 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C130" t="str">
         <v>Béton</v>
@@ -5704,17 +5704,17 @@
       <c r="E130" t="str">
         <v>m3</v>
       </c>
-      <c r="F130">
+      <c r="F130" t="str">
         <v>93509</v>
       </c>
       <c r="G130" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H130" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I130" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J130" t="str">
         <v>14/10/2026</v>
@@ -5734,7 +5734,7 @@
         <v>BET-450CPJ</v>
       </c>
       <c r="B131" t="str">
-        <v>Béton fabriqué chantier dosé 450 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 450 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C131" t="str">
         <v>Béton</v>
@@ -5745,17 +5745,17 @@
       <c r="E131" t="str">
         <v>m3</v>
       </c>
-      <c r="F131">
+      <c r="F131" t="str">
         <v>100042</v>
       </c>
       <c r="G131" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H131" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I131" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J131" t="str">
         <v>14/10/2026</v>
@@ -5775,7 +5775,7 @@
         <v>BET-500CPJ</v>
       </c>
       <c r="B132" t="str">
-        <v>Béton fabriqué chantier dosé 500 kg/m3, CPJ 42,5</v>
+        <v>"Béton fabriqué chantier dosé 500 kg/m3, CPJ 42,5"</v>
       </c>
       <c r="C132" t="str">
         <v>Béton</v>
@@ -5786,17 +5786,17 @@
       <c r="E132" t="str">
         <v>m3</v>
       </c>
-      <c r="F132">
+      <c r="F132" t="str">
         <v>106572</v>
       </c>
       <c r="G132" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H132" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I132" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J132" t="str">
         <v>14/10/2026</v>
@@ -5816,7 +5816,7 @@
         <v>BET-150CPJ32</v>
       </c>
       <c r="B133" t="str">
-        <v>Béton fabriqué chantier dosé 150 kg/m3, CPJ 32,5</v>
+        <v>"Béton fabriqué chantier dosé 150 kg/m3, CPJ 32,5"</v>
       </c>
       <c r="C133" t="str">
         <v>Béton</v>
@@ -5827,17 +5827,17 @@
       <c r="E133" t="str">
         <v>m3</v>
       </c>
-      <c r="F133">
+      <c r="F133" t="str">
         <v>60335</v>
       </c>
       <c r="G133" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H133" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I133" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J133" t="str">
         <v>14/10/2026</v>
@@ -5857,7 +5857,7 @@
         <v>BET-350CPJ32</v>
       </c>
       <c r="B134" t="str">
-        <v>Béton fabriqué chantier dosé 350 kg/m3, CPJ 32,5</v>
+        <v>"Béton fabriqué chantier dosé 350 kg/m3, CPJ 32,5"</v>
       </c>
       <c r="C134" t="str">
         <v>Béton</v>
@@ -5868,17 +5868,17 @@
       <c r="E134" t="str">
         <v>m3</v>
       </c>
-      <c r="F134">
+      <c r="F134" t="str">
         <v>85882</v>
       </c>
       <c r="G134" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H134" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I134" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J134" t="str">
         <v>14/10/2026</v>
@@ -5898,7 +5898,7 @@
         <v>BET-500CPJ32</v>
       </c>
       <c r="B135" t="str">
-        <v>Béton fabriqué chantier dosé 500 kg/m3, CPJ 32,5</v>
+        <v>"Béton fabriqué chantier dosé 500 kg/m3, CPJ 32,5"</v>
       </c>
       <c r="C135" t="str">
         <v>Béton</v>
@@ -5909,17 +5909,17 @@
       <c r="E135" t="str">
         <v>m3</v>
       </c>
-      <c r="F135">
+      <c r="F135" t="str">
         <v>105008</v>
       </c>
       <c r="G135" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H135" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I135" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J135" t="str">
         <v>14/10/2026</v>
@@ -5939,7 +5939,7 @@
         <v>BET-E1</v>
       </c>
       <c r="B136" t="str">
-        <v>Béton dosé 350 kg/m3 CPA 42,5, élévation poteaux</v>
+        <v>"Béton dosé 350 kg/m3 CPA 42,5, élévation poteaux"</v>
       </c>
       <c r="C136" t="str">
         <v>Béton</v>
@@ -5950,17 +5950,17 @@
       <c r="E136" t="str">
         <v>m3</v>
       </c>
-      <c r="F136">
+      <c r="F136" t="str">
         <v>99148</v>
       </c>
       <c r="G136" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H136" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I136" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J136" t="str">
         <v>14/10/2026</v>
@@ -5980,7 +5980,7 @@
         <v>BET-E2</v>
       </c>
       <c r="B137" t="str">
-        <v>Béton dosé 350 kg/m3 CPA 42,5, élévation poutres</v>
+        <v>"Béton dosé 350 kg/m3 CPA 42,5, élévation poutres"</v>
       </c>
       <c r="C137" t="str">
         <v>Béton</v>
@@ -5991,17 +5991,17 @@
       <c r="E137" t="str">
         <v>m3</v>
       </c>
-      <c r="F137">
+      <c r="F137" t="str">
         <v>98425</v>
       </c>
       <c r="G137" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H137" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I137" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J137" t="str">
         <v>14/10/2026</v>
@@ -6021,7 +6021,7 @@
         <v>BET-E3</v>
       </c>
       <c r="B138" t="str">
-        <v>Béton dosé 350 kg/m3 CPA 42,5, élévation dalle pleine</v>
+        <v>"Béton dosé 350 kg/m3 CPA 42,5, élévation dalle pleine"</v>
       </c>
       <c r="C138" t="str">
         <v>Béton</v>
@@ -6032,17 +6032,17 @@
       <c r="E138" t="str">
         <v>m3</v>
       </c>
-      <c r="F138">
+      <c r="F138" t="str">
         <v>97109</v>
       </c>
       <c r="G138" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H138" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I138" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J138" t="str">
         <v>14/10/2026</v>
@@ -6062,7 +6062,7 @@
         <v>BET-E4</v>
       </c>
       <c r="B139" t="str">
-        <v>Béton dosé 350 kg/m3 CPA 42,5, élévation escaliers</v>
+        <v>"Béton dosé 350 kg/m3 CPA 42,5, élévation escaliers"</v>
       </c>
       <c r="C139" t="str">
         <v>Béton</v>
@@ -6073,17 +6073,17 @@
       <c r="E139" t="str">
         <v>m3</v>
       </c>
-      <c r="F139">
+      <c r="F139" t="str">
         <v>100562</v>
       </c>
       <c r="G139" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H139" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I139" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J139" t="str">
         <v>14/10/2026</v>
@@ -6103,7 +6103,7 @@
         <v>BET-E5</v>
       </c>
       <c r="B140" t="str">
-        <v>Béton dosé 350 kg/m3 CPA 42,5, élévation voiles</v>
+        <v>"Béton dosé 350 kg/m3 CPA 42,5, élévation voiles"</v>
       </c>
       <c r="C140" t="str">
         <v>Béton</v>
@@ -6114,17 +6114,17 @@
       <c r="E140" t="str">
         <v>m3</v>
       </c>
-      <c r="F140">
+      <c r="F140" t="str">
         <v>96781</v>
       </c>
       <c r="G140" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H140" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I140" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J140" t="str">
         <v>14/10/2026</v>
@@ -6144,7 +6144,7 @@
         <v>BET-E6</v>
       </c>
       <c r="B141" t="str">
-        <v>Béton dosé 350 kg/m3 CPJ 42,5, élévation poteaux</v>
+        <v>"Béton dosé 350 kg/m3 CPJ 42,5, élévation poteaux"</v>
       </c>
       <c r="C141" t="str">
         <v>Béton</v>
@@ -6155,17 +6155,17 @@
       <c r="E141" t="str">
         <v>m3</v>
       </c>
-      <c r="F141">
+      <c r="F141" t="str">
         <v>91754</v>
       </c>
       <c r="G141" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H141" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I141" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J141" t="str">
         <v>14/10/2026</v>
@@ -6185,7 +6185,7 @@
         <v>BET-E7</v>
       </c>
       <c r="B142" t="str">
-        <v>Béton dosé 350 kg/m3 CPJ 42,5, élévation poutres</v>
+        <v>"Béton dosé 350 kg/m3 CPJ 42,5, élévation poutres"</v>
       </c>
       <c r="C142" t="str">
         <v>Béton</v>
@@ -6196,17 +6196,17 @@
       <c r="E142" t="str">
         <v>m3</v>
       </c>
-      <c r="F142">
+      <c r="F142" t="str">
         <v>91033</v>
       </c>
       <c r="G142" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H142" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I142" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J142" t="str">
         <v>14/10/2026</v>
@@ -6226,7 +6226,7 @@
         <v>BET-E8</v>
       </c>
       <c r="B143" t="str">
-        <v>Béton dosé 350 kg/m3 CPJ 42,5, élévation dalle pleine</v>
+        <v>"Béton dosé 350 kg/m3 CPJ 42,5, élévation dalle pleine"</v>
       </c>
       <c r="C143" t="str">
         <v>Béton</v>
@@ -6237,17 +6237,17 @@
       <c r="E143" t="str">
         <v>m3</v>
       </c>
-      <c r="F143">
+      <c r="F143" t="str">
         <v>89717</v>
       </c>
       <c r="G143" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H143" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I143" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J143" t="str">
         <v>14/10/2026</v>
@@ -6267,7 +6267,7 @@
         <v>BET-E9</v>
       </c>
       <c r="B144" t="str">
-        <v>Béton dosé 350 kg/m3 CPJ 42,5, élévation voiles</v>
+        <v>"Béton dosé 350 kg/m3 CPJ 42,5, élévation voiles"</v>
       </c>
       <c r="C144" t="str">
         <v>Béton</v>
@@ -6278,17 +6278,17 @@
       <c r="E144" t="str">
         <v>m3</v>
       </c>
-      <c r="F144">
+      <c r="F144" t="str">
         <v>89390</v>
       </c>
       <c r="G144" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H144" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I144" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J144" t="str">
         <v>14/10/2026</v>
@@ -6308,7 +6308,7 @@
         <v>AGG-01</v>
       </c>
       <c r="B145" t="str">
-        <v>Agglo plein 20 cm CPA 42,5</v>
+        <v>"Agglo plein 20 cm CPA 42,5"</v>
       </c>
       <c r="C145" t="str">
         <v>Maçonnerie</v>
@@ -6319,17 +6319,17 @@
       <c r="E145" t="str">
         <v>m2</v>
       </c>
-      <c r="F145">
+      <c r="F145" t="str">
         <v>19428</v>
       </c>
       <c r="G145" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H145" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I145" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J145" t="str">
         <v>14/10/2026</v>
@@ -6349,7 +6349,7 @@
         <v>AGG-02</v>
       </c>
       <c r="B146" t="str">
-        <v>Agglo plein 15 cm CPA 42,5</v>
+        <v>"Agglo plein 15 cm CPA 42,5"</v>
       </c>
       <c r="C146" t="str">
         <v>Maçonnerie</v>
@@ -6360,17 +6360,17 @@
       <c r="E146" t="str">
         <v>m2</v>
       </c>
-      <c r="F146">
+      <c r="F146" t="str">
         <v>14754</v>
       </c>
       <c r="G146" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H146" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I146" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J146" t="str">
         <v>14/10/2026</v>
@@ -6390,7 +6390,7 @@
         <v>AGG-03</v>
       </c>
       <c r="B147" t="str">
-        <v>Agglo plein 10 cm CPA 42,5</v>
+        <v>"Agglo plein 10 cm CPA 42,5"</v>
       </c>
       <c r="C147" t="str">
         <v>Maçonnerie</v>
@@ -6401,17 +6401,17 @@
       <c r="E147" t="str">
         <v>m2</v>
       </c>
-      <c r="F147">
+      <c r="F147" t="str">
         <v>10516</v>
       </c>
       <c r="G147" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H147" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I147" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J147" t="str">
         <v>14/10/2026</v>
@@ -6431,7 +6431,7 @@
         <v>AGG-04</v>
       </c>
       <c r="B148" t="str">
-        <v>Agglo plein 7 cm CPA 42,5</v>
+        <v>"Agglo plein 7 cm CPA 42,5"</v>
       </c>
       <c r="C148" t="str">
         <v>Maçonnerie</v>
@@ -6442,17 +6442,17 @@
       <c r="E148" t="str">
         <v>m2</v>
       </c>
-      <c r="F148">
+      <c r="F148" t="str">
         <v>7103</v>
       </c>
       <c r="G148" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H148" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I148" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J148" t="str">
         <v>14/10/2026</v>
@@ -6472,7 +6472,7 @@
         <v>AGG-05</v>
       </c>
       <c r="B149" t="str">
-        <v>Agglo creux 20 cm CPA 42,5</v>
+        <v>"Agglo creux 20 cm CPA 42,5"</v>
       </c>
       <c r="C149" t="str">
         <v>Maçonnerie</v>
@@ -6483,17 +6483,17 @@
       <c r="E149" t="str">
         <v>m2</v>
       </c>
-      <c r="F149">
+      <c r="F149" t="str">
         <v>11919</v>
       </c>
       <c r="G149" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H149" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I149" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J149" t="str">
         <v>14/10/2026</v>
@@ -6513,7 +6513,7 @@
         <v>AGG-06</v>
       </c>
       <c r="B150" t="str">
-        <v>Agglo creux 15 cm CPA 42,5</v>
+        <v>"Agglo creux 15 cm CPA 42,5"</v>
       </c>
       <c r="C150" t="str">
         <v>Maçonnerie</v>
@@ -6524,17 +6524,17 @@
       <c r="E150" t="str">
         <v>m2</v>
       </c>
-      <c r="F150">
+      <c r="F150" t="str">
         <v>9402</v>
       </c>
       <c r="G150" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H150" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I150" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J150" t="str">
         <v>14/10/2026</v>
@@ -6554,7 +6554,7 @@
         <v>AGG-07</v>
       </c>
       <c r="B151" t="str">
-        <v>Agglo creux 12 cm CPA 42,5</v>
+        <v>"Agglo creux 12 cm CPA 42,5"</v>
       </c>
       <c r="C151" t="str">
         <v>Maçonnerie</v>
@@ -6565,17 +6565,17 @@
       <c r="E151" t="str">
         <v>m2</v>
       </c>
-      <c r="F151">
+      <c r="F151" t="str">
         <v>8813</v>
       </c>
       <c r="G151" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H151" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I151" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J151" t="str">
         <v>14/10/2026</v>
@@ -6595,7 +6595,7 @@
         <v>AGG-08</v>
       </c>
       <c r="B152" t="str">
-        <v>Agglo creux 10 cm CPA 42,5</v>
+        <v>"Agglo creux 10 cm CPA 42,5"</v>
       </c>
       <c r="C152" t="str">
         <v>Maçonnerie</v>
@@ -6606,17 +6606,17 @@
       <c r="E152" t="str">
         <v>m2</v>
       </c>
-      <c r="F152">
+      <c r="F152" t="str">
         <v>8274</v>
       </c>
       <c r="G152" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H152" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I152" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J152" t="str">
         <v>14/10/2026</v>
@@ -6636,7 +6636,7 @@
         <v>AGG-09</v>
       </c>
       <c r="B153" t="str">
-        <v>Agglo creux 7 cm CPA 42,5</v>
+        <v>"Agglo creux 7 cm CPA 42,5"</v>
       </c>
       <c r="C153" t="str">
         <v>Maçonnerie</v>
@@ -6647,17 +6647,17 @@
       <c r="E153" t="str">
         <v>m2</v>
       </c>
-      <c r="F153">
+      <c r="F153" t="str">
         <v>6085</v>
       </c>
       <c r="G153" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H153" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I153" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J153" t="str">
         <v>14/10/2026</v>
@@ -6677,7 +6677,7 @@
         <v>AGG-10</v>
       </c>
       <c r="B154" t="str">
-        <v>Agglo plein 20 cm CPJ 42,5</v>
+        <v>"Agglo plein 20 cm CPJ 42,5"</v>
       </c>
       <c r="C154" t="str">
         <v>Maçonnerie</v>
@@ -6688,17 +6688,17 @@
       <c r="E154" t="str">
         <v>m2</v>
       </c>
-      <c r="F154">
+      <c r="F154" t="str">
         <v>18293</v>
       </c>
       <c r="G154" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H154" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I154" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J154" t="str">
         <v>14/10/2026</v>
@@ -6718,7 +6718,7 @@
         <v>AGG-11</v>
       </c>
       <c r="B155" t="str">
-        <v>Agglo plein 15 cm CPJ 42,5</v>
+        <v>"Agglo plein 15 cm CPJ 42,5"</v>
       </c>
       <c r="C155" t="str">
         <v>Maçonnerie</v>
@@ -6729,17 +6729,17 @@
       <c r="E155" t="str">
         <v>m2</v>
       </c>
-      <c r="F155">
+      <c r="F155" t="str">
         <v>13911</v>
       </c>
       <c r="G155" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H155" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I155" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J155" t="str">
         <v>14/10/2026</v>
@@ -6759,7 +6759,7 @@
         <v>AGG-12</v>
       </c>
       <c r="B156" t="str">
-        <v>Agglo plein 10 cm CPJ 42,5</v>
+        <v>"Agglo plein 10 cm CPJ 42,5"</v>
       </c>
       <c r="C156" t="str">
         <v>Maçonnerie</v>
@@ -6770,17 +6770,17 @@
       <c r="E156" t="str">
         <v>m2</v>
       </c>
-      <c r="F156">
+      <c r="F156" t="str">
         <v>9952</v>
       </c>
       <c r="G156" t="str">
         <v>Abidjan</v>
       </c>
       <c r="H156" t="str">
-        <v>Guide BTP-PRIX</v>
+        <v>Marché ivoirien</v>
       </c>
       <c r="I156" t="str">
-        <v>BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd</v>
+        <v>"BTP-PRIX (guide tarifaire ICOS Abidjan), via Scribd"</v>
       </c>
       <c r="J156" t="str">
         <v>14/10/2026</v>
@@ -6800,7 +6800,7 @@
         <v>ACI-01</v>
       </c>
       <c r="B157" t="str">
-        <v>Barre HA Ø8 (acier à béton)</v>
+        <v>"Barre HA Ø8 (acier à béton)"</v>
       </c>
       <c r="C157" t="str">
         <v>Acier</v>
@@ -6811,7 +6811,7 @@
       <c r="E157" t="str">
         <v>kg</v>
       </c>
-      <c r="F157">
+      <c r="F157" t="str">
         <v>3200</v>
       </c>
       <c r="G157" t="str">
@@ -6821,7 +6821,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I157" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J157" t="str">
         <v>2026-10-16</v>
@@ -6833,7 +6833,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M157" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -6841,7 +6841,7 @@
         <v>ACI-02</v>
       </c>
       <c r="B158" t="str">
-        <v>Barre HA Ø10 (acier à béton)</v>
+        <v>"Barre HA Ø10 (acier à béton)"</v>
       </c>
       <c r="C158" t="str">
         <v>Acier</v>
@@ -6852,7 +6852,7 @@
       <c r="E158" t="str">
         <v>kg</v>
       </c>
-      <c r="F158">
+      <c r="F158" t="str">
         <v>3300</v>
       </c>
       <c r="G158" t="str">
@@ -6862,7 +6862,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I158" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J158" t="str">
         <v>2026-10-16</v>
@@ -6874,7 +6874,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M158" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -6882,7 +6882,7 @@
         <v>ACI-03</v>
       </c>
       <c r="B159" t="str">
-        <v>Barre HA Ø12 (acier à béton)</v>
+        <v>"Barre HA Ø12 (acier à béton)"</v>
       </c>
       <c r="C159" t="str">
         <v>Acier</v>
@@ -6893,7 +6893,7 @@
       <c r="E159" t="str">
         <v>kg</v>
       </c>
-      <c r="F159">
+      <c r="F159" t="str">
         <v>3400</v>
       </c>
       <c r="G159" t="str">
@@ -6903,7 +6903,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I159" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J159" t="str">
         <v>2026-10-16</v>
@@ -6915,7 +6915,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M159" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -6923,7 +6923,7 @@
         <v>ACI-04</v>
       </c>
       <c r="B160" t="str">
-        <v>Barre HA Ø14 (acier à béton)</v>
+        <v>"Barre HA Ø14 (acier à béton)"</v>
       </c>
       <c r="C160" t="str">
         <v>Acier</v>
@@ -6934,7 +6934,7 @@
       <c r="E160" t="str">
         <v>kg</v>
       </c>
-      <c r="F160">
+      <c r="F160" t="str">
         <v>3500</v>
       </c>
       <c r="G160" t="str">
@@ -6944,7 +6944,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I160" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J160" t="str">
         <v>2026-10-16</v>
@@ -6956,7 +6956,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M160" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -6964,7 +6964,7 @@
         <v>ACI-05</v>
       </c>
       <c r="B161" t="str">
-        <v>Barre HA Ø16 (acier à béton)</v>
+        <v>"Barre HA Ø16 (acier à béton)"</v>
       </c>
       <c r="C161" t="str">
         <v>Acier</v>
@@ -6975,7 +6975,7 @@
       <c r="E161" t="str">
         <v>kg</v>
       </c>
-      <c r="F161">
+      <c r="F161" t="str">
         <v>3600</v>
       </c>
       <c r="G161" t="str">
@@ -6985,7 +6985,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I161" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J161" t="str">
         <v>2026-10-16</v>
@@ -6997,7 +6997,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M161" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -7005,7 +7005,7 @@
         <v>ACI-06</v>
       </c>
       <c r="B162" t="str">
-        <v>Barre HA Ø20 (acier à béton)</v>
+        <v>"Barre HA Ø20 (acier à béton)"</v>
       </c>
       <c r="C162" t="str">
         <v>Acier</v>
@@ -7016,7 +7016,7 @@
       <c r="E162" t="str">
         <v>kg</v>
       </c>
-      <c r="F162">
+      <c r="F162" t="str">
         <v>3700</v>
       </c>
       <c r="G162" t="str">
@@ -7026,7 +7026,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I162" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J162" t="str">
         <v>2026-10-16</v>
@@ -7038,7 +7038,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M162" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -7046,7 +7046,7 @@
         <v>ACI-07</v>
       </c>
       <c r="B163" t="str">
-        <v>Barre HA Ø25 (acier à béton)</v>
+        <v>"Barre HA Ø25 (acier à béton)"</v>
       </c>
       <c r="C163" t="str">
         <v>Acier</v>
@@ -7057,7 +7057,7 @@
       <c r="E163" t="str">
         <v>kg</v>
       </c>
-      <c r="F163">
+      <c r="F163" t="str">
         <v>3800</v>
       </c>
       <c r="G163" t="str">
@@ -7067,7 +7067,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I163" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J163" t="str">
         <v>2026-10-16</v>
@@ -7079,7 +7079,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M163" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -7087,7 +7087,7 @@
         <v>ACI-08</v>
       </c>
       <c r="B164" t="str">
-        <v>Treillis soudé (panneau)</v>
+        <v>"Treillis soudé (panneau)"</v>
       </c>
       <c r="C164" t="str">
         <v>Acier</v>
@@ -7098,7 +7098,7 @@
       <c r="E164" t="str">
         <v>m2</v>
       </c>
-      <c r="F164">
+      <c r="F164" t="str">
         <v>4500</v>
       </c>
       <c r="G164" t="str">
@@ -7108,7 +7108,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I164" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J164" t="str">
         <v>2026-10-16</v>
@@ -7120,7 +7120,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M164" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -7128,7 +7128,7 @@
         <v>ACI-09</v>
       </c>
       <c r="B165" t="str">
-        <v>Fil d'attache recuit (kg)</v>
+        <v>"Fil d'attache recuit (kg)"</v>
       </c>
       <c r="C165" t="str">
         <v>Acier</v>
@@ -7139,7 +7139,7 @@
       <c r="E165" t="str">
         <v>kg</v>
       </c>
-      <c r="F165">
+      <c r="F165" t="str">
         <v>1200</v>
       </c>
       <c r="G165" t="str">
@@ -7149,7 +7149,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I165" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J165" t="str">
         <v>2026-10-16</v>
@@ -7161,7 +7161,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M165" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -7169,7 +7169,7 @@
         <v>ACI-10</v>
       </c>
       <c r="B166" t="str">
-        <v>Acier pour fondations (kg)</v>
+        <v>"Acier pour fondations (kg)"</v>
       </c>
       <c r="C166" t="str">
         <v>Acier</v>
@@ -7180,7 +7180,7 @@
       <c r="E166" t="str">
         <v>kg</v>
       </c>
-      <c r="F166">
+      <c r="F166" t="str">
         <v>3500</v>
       </c>
       <c r="G166" t="str">
@@ -7190,7 +7190,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I166" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J166" t="str">
         <v>2026-10-16</v>
@@ -7202,7 +7202,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M166" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -7210,7 +7210,7 @@
         <v>ACI-11</v>
       </c>
       <c r="B167" t="str">
-        <v>Acier pour poutres et poteaux (kg)</v>
+        <v>"Acier pour poutres et poteaux (kg)"</v>
       </c>
       <c r="C167" t="str">
         <v>Acier</v>
@@ -7221,7 +7221,7 @@
       <c r="E167" t="str">
         <v>kg</v>
       </c>
-      <c r="F167">
+      <c r="F167" t="str">
         <v>3600</v>
       </c>
       <c r="G167" t="str">
@@ -7231,7 +7231,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I167" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J167" t="str">
         <v>2026-10-16</v>
@@ -7243,7 +7243,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M167" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -7251,7 +7251,7 @@
         <v>BIT-01</v>
       </c>
       <c r="B168" t="str">
-        <v>Bitume 60/70 (vrac)</v>
+        <v>"Bitume 60/70 (vrac)"</v>
       </c>
       <c r="C168" t="str">
         <v>Bitume et routes</v>
@@ -7262,7 +7262,7 @@
       <c r="E168" t="str">
         <v>t</v>
       </c>
-      <c r="F168">
+      <c r="F168" t="str">
         <v>420000</v>
       </c>
       <c r="G168" t="str">
@@ -7272,7 +7272,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I168" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J168" t="str">
         <v>2026-10-16</v>
@@ -7284,7 +7284,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M168" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -7292,7 +7292,7 @@
         <v>BIT-02</v>
       </c>
       <c r="B169" t="str">
-        <v>Enrobé bitumineux à chaud (EB)</v>
+        <v>"Enrobé bitumineux à chaud (EB)"</v>
       </c>
       <c r="C169" t="str">
         <v>Bitume et routes</v>
@@ -7303,7 +7303,7 @@
       <c r="E169" t="str">
         <v>t</v>
       </c>
-      <c r="F169">
+      <c r="F169" t="str">
         <v>95000</v>
       </c>
       <c r="G169" t="str">
@@ -7313,7 +7313,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I169" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J169" t="str">
         <v>2026-10-16</v>
@@ -7325,7 +7325,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M169" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -7333,7 +7333,7 @@
         <v>BIT-03</v>
       </c>
       <c r="B170" t="str">
-        <v>Grave bitume (GB) 0/20</v>
+        <v>"Grave bitume (GB) 0/20"</v>
       </c>
       <c r="C170" t="str">
         <v>Bitume et routes</v>
@@ -7344,7 +7344,7 @@
       <c r="E170" t="str">
         <v>m3</v>
       </c>
-      <c r="F170">
+      <c r="F170" t="str">
         <v>48000</v>
       </c>
       <c r="G170" t="str">
@@ -7354,7 +7354,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I170" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J170" t="str">
         <v>2026-10-16</v>
@@ -7366,7 +7366,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M170" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -7374,7 +7374,7 @@
         <v>BIT-04</v>
       </c>
       <c r="B171" t="str">
-        <v>Enduit superficiel (couche d'accrochage)</v>
+        <v>"Enduit superficiel (couche d'accrochage)"</v>
       </c>
       <c r="C171" t="str">
         <v>Bitume et routes</v>
@@ -7385,7 +7385,7 @@
       <c r="E171" t="str">
         <v>m2</v>
       </c>
-      <c r="F171">
+      <c r="F171" t="str">
         <v>3500</v>
       </c>
       <c r="G171" t="str">
@@ -7395,7 +7395,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I171" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J171" t="str">
         <v>2026-10-16</v>
@@ -7407,7 +7407,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M171" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -7415,7 +7415,7 @@
         <v>BIT-05</v>
       </c>
       <c r="B172" t="str">
-        <v>Couche de base (latérite améliorée)</v>
+        <v>"Couche de base (latérite améliorée)"</v>
       </c>
       <c r="C172" t="str">
         <v>Bitume et routes</v>
@@ -7426,7 +7426,7 @@
       <c r="E172" t="str">
         <v>m3</v>
       </c>
-      <c r="F172">
+      <c r="F172" t="str">
         <v>28000</v>
       </c>
       <c r="G172" t="str">
@@ -7436,7 +7436,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I172" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J172" t="str">
         <v>2026-10-16</v>
@@ -7448,7 +7448,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M172" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -7456,7 +7456,7 @@
         <v>BIT-06</v>
       </c>
       <c r="B173" t="str">
-        <v>Couche de fondation (matériau sélectionné)</v>
+        <v>"Couche de fondation (matériau sélectionné)"</v>
       </c>
       <c r="C173" t="str">
         <v>Bitume et routes</v>
@@ -7467,7 +7467,7 @@
       <c r="E173" t="str">
         <v>m3</v>
       </c>
-      <c r="F173">
+      <c r="F173" t="str">
         <v>22000</v>
       </c>
       <c r="G173" t="str">
@@ -7477,7 +7477,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I173" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J173" t="str">
         <v>2026-10-16</v>
@@ -7489,7 +7489,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M173" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -7497,7 +7497,7 @@
         <v>BIT-07</v>
       </c>
       <c r="B174" t="str">
-        <v>Bordure en béton (ml)</v>
+        <v>"Bordure en béton (ml)"</v>
       </c>
       <c r="C174" t="str">
         <v>Bitume et routes</v>
@@ -7508,7 +7508,7 @@
       <c r="E174" t="str">
         <v>ml</v>
       </c>
-      <c r="F174">
+      <c r="F174" t="str">
         <v>12000</v>
       </c>
       <c r="G174" t="str">
@@ -7518,7 +7518,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I174" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J174" t="str">
         <v>2026-10-16</v>
@@ -7530,7 +7530,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M174" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -7538,7 +7538,7 @@
         <v>BIT-08</v>
       </c>
       <c r="B175" t="str">
-        <v>Caniveau préfabriqué (ml)</v>
+        <v>"Caniveau préfabriqué (ml)"</v>
       </c>
       <c r="C175" t="str">
         <v>Bitume et routes</v>
@@ -7549,7 +7549,7 @@
       <c r="E175" t="str">
         <v>ml</v>
       </c>
-      <c r="F175">
+      <c r="F175" t="str">
         <v>18000</v>
       </c>
       <c r="G175" t="str">
@@ -7559,7 +7559,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I175" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J175" t="str">
         <v>2026-10-16</v>
@@ -7571,7 +7571,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M175" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -7579,7 +7579,7 @@
         <v>BIT-09</v>
       </c>
       <c r="B176" t="str">
-        <v>Marquage routier (peinture thermoplastique)</v>
+        <v>"Marquage routier (peinture thermoplastique)"</v>
       </c>
       <c r="C176" t="str">
         <v>Bitume et routes</v>
@@ -7590,7 +7590,7 @@
       <c r="E176" t="str">
         <v>m2</v>
       </c>
-      <c r="F176">
+      <c r="F176" t="str">
         <v>2500</v>
       </c>
       <c r="G176" t="str">
@@ -7600,7 +7600,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I176" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J176" t="str">
         <v>2026-10-16</v>
@@ -7612,7 +7612,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M176" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -7620,7 +7620,7 @@
         <v>BIT-10</v>
       </c>
       <c r="B177" t="str">
-        <v>Panneau de signalisation (u)</v>
+        <v>"Panneau de signalisation (u)"</v>
       </c>
       <c r="C177" t="str">
         <v>Bitume et routes</v>
@@ -7631,7 +7631,7 @@
       <c r="E177" t="str">
         <v>u</v>
       </c>
-      <c r="F177">
+      <c r="F177" t="str">
         <v>85000</v>
       </c>
       <c r="G177" t="str">
@@ -7641,7 +7641,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I177" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J177" t="str">
         <v>2026-10-16</v>
@@ -7653,7 +7653,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M177" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -7661,7 +7661,7 @@
         <v>BOI-01</v>
       </c>
       <c r="B178" t="str">
-        <v>Bois de coffrage (sapin)</v>
+        <v>"Bois de coffrage (sapin)"</v>
       </c>
       <c r="C178" t="str">
         <v>Bois et coffrage</v>
@@ -7672,7 +7672,7 @@
       <c r="E178" t="str">
         <v>m3</v>
       </c>
-      <c r="F178">
+      <c r="F178" t="str">
         <v>180000</v>
       </c>
       <c r="G178" t="str">
@@ -7682,7 +7682,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I178" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J178" t="str">
         <v>2026-10-16</v>
@@ -7694,7 +7694,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M178" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -7702,7 +7702,7 @@
         <v>BOI-02</v>
       </c>
       <c r="B179" t="str">
-        <v>Bois de charpente (chêne/iroko)</v>
+        <v>"Bois de charpente (chêne/iroko)"</v>
       </c>
       <c r="C179" t="str">
         <v>Bois et coffrage</v>
@@ -7713,7 +7713,7 @@
       <c r="E179" t="str">
         <v>m3</v>
       </c>
-      <c r="F179">
+      <c r="F179" t="str">
         <v>220000</v>
       </c>
       <c r="G179" t="str">
@@ -7723,7 +7723,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I179" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J179" t="str">
         <v>2026-10-16</v>
@@ -7735,7 +7735,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M179" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -7743,7 +7743,7 @@
         <v>BOI-03</v>
       </c>
       <c r="B180" t="str">
-        <v>Planche de coffrage 27 mm</v>
+        <v>"Planche de coffrage 27 mm"</v>
       </c>
       <c r="C180" t="str">
         <v>Bois et coffrage</v>
@@ -7754,7 +7754,7 @@
       <c r="E180" t="str">
         <v>m3</v>
       </c>
-      <c r="F180">
+      <c r="F180" t="str">
         <v>175000</v>
       </c>
       <c r="G180" t="str">
@@ -7764,7 +7764,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I180" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J180" t="str">
         <v>2026-10-16</v>
@@ -7776,7 +7776,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M180" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -7784,7 +7784,7 @@
         <v>BOI-04</v>
       </c>
       <c r="B181" t="str">
-        <v>Chevrons (bois)</v>
+        <v>"Chevrons (bois)"</v>
       </c>
       <c r="C181" t="str">
         <v>Bois et coffrage</v>
@@ -7795,7 +7795,7 @@
       <c r="E181" t="str">
         <v>ml</v>
       </c>
-      <c r="F181">
+      <c r="F181" t="str">
         <v>2500</v>
       </c>
       <c r="G181" t="str">
@@ -7805,7 +7805,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I181" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J181" t="str">
         <v>2026-10-16</v>
@@ -7817,7 +7817,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M181" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -7825,7 +7825,7 @@
         <v>BOI-05</v>
       </c>
       <c r="B182" t="str">
-        <v>Volige (bois)</v>
+        <v>"Volige (bois)"</v>
       </c>
       <c r="C182" t="str">
         <v>Bois et coffrage</v>
@@ -7836,7 +7836,7 @@
       <c r="E182" t="str">
         <v>m2</v>
       </c>
-      <c r="F182">
+      <c r="F182" t="str">
         <v>8000</v>
       </c>
       <c r="G182" t="str">
@@ -7846,7 +7846,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I182" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J182" t="str">
         <v>2026-10-16</v>
@@ -7858,7 +7858,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M182" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -7866,7 +7866,7 @@
         <v>BOI-06</v>
       </c>
       <c r="B183" t="str">
-        <v>Contreplaqué marine (m²)</v>
+        <v>"Contreplaqué marine (m²)"</v>
       </c>
       <c r="C183" t="str">
         <v>Bois et coffrage</v>
@@ -7877,7 +7877,7 @@
       <c r="E183" t="str">
         <v>m2</v>
       </c>
-      <c r="F183">
+      <c r="F183" t="str">
         <v>12000</v>
       </c>
       <c r="G183" t="str">
@@ -7887,7 +7887,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I183" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J183" t="str">
         <v>2026-10-16</v>
@@ -7899,7 +7899,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M183" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -7907,7 +7907,7 @@
         <v>BOI-07</v>
       </c>
       <c r="B184" t="str">
-        <v>Tasseaux et liteaux (ml)</v>
+        <v>"Tasseaux et liteaux (ml)"</v>
       </c>
       <c r="C184" t="str">
         <v>Bois et coffrage</v>
@@ -7918,7 +7918,7 @@
       <c r="E184" t="str">
         <v>ml</v>
       </c>
-      <c r="F184">
+      <c r="F184" t="str">
         <v>800</v>
       </c>
       <c r="G184" t="str">
@@ -7928,7 +7928,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I184" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J184" t="str">
         <v>2026-10-16</v>
@@ -7940,7 +7940,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M184" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -7948,7 +7948,7 @@
         <v>CLIM-01</v>
       </c>
       <c r="B185" t="str">
-        <v>Climatiseur split 12000 BTU (u)</v>
+        <v>"Climatiseur split 12000 BTU (u)"</v>
       </c>
       <c r="C185" t="str">
         <v>Climatisation et ventilation</v>
@@ -7959,7 +7959,7 @@
       <c r="E185" t="str">
         <v>u</v>
       </c>
-      <c r="F185">
+      <c r="F185" t="str">
         <v>320000</v>
       </c>
       <c r="G185" t="str">
@@ -7969,7 +7969,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I185" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J185" t="str">
         <v>2026-10-16</v>
@@ -7981,7 +7981,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M185" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -7989,7 +7989,7 @@
         <v>CLIM-02</v>
       </c>
       <c r="B186" t="str">
-        <v>Gaines et accessoires ventilation (ml)</v>
+        <v>"Gaines et accessoires ventilation (ml)"</v>
       </c>
       <c r="C186" t="str">
         <v>Climatisation et ventilation</v>
@@ -8000,7 +8000,7 @@
       <c r="E186" t="str">
         <v>ml</v>
       </c>
-      <c r="F186">
+      <c r="F186" t="str">
         <v>3500</v>
       </c>
       <c r="G186" t="str">
@@ -8010,7 +8010,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I186" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J186" t="str">
         <v>2026-10-16</v>
@@ -8022,7 +8022,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M186" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -8030,7 +8030,7 @@
         <v>COUV-01</v>
       </c>
       <c r="B187" t="str">
-        <v>Tôle ondulée galvanisée (m²)</v>
+        <v>"Tôle ondulée galvanisée (m²)"</v>
       </c>
       <c r="C187" t="str">
         <v>Couverture</v>
@@ -8041,7 +8041,7 @@
       <c r="E187" t="str">
         <v>m2</v>
       </c>
-      <c r="F187">
+      <c r="F187" t="str">
         <v>7500</v>
       </c>
       <c r="G187" t="str">
@@ -8051,7 +8051,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I187" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J187" t="str">
         <v>2026-10-16</v>
@@ -8063,7 +8063,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M187" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -8071,7 +8071,7 @@
         <v>COUV-02</v>
       </c>
       <c r="B188" t="str">
-        <v>Tôle bac acier (m²)</v>
+        <v>"Tôle bac acier (m²)"</v>
       </c>
       <c r="C188" t="str">
         <v>Couverture</v>
@@ -8082,7 +8082,7 @@
       <c r="E188" t="str">
         <v>m2</v>
       </c>
-      <c r="F188">
+      <c r="F188" t="str">
         <v>9000</v>
       </c>
       <c r="G188" t="str">
@@ -8092,7 +8092,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I188" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J188" t="str">
         <v>2026-10-16</v>
@@ -8104,7 +8104,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M188" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -8112,7 +8112,7 @@
         <v>COUV-03</v>
       </c>
       <c r="B189" t="str">
-        <v>Tuile béton (u)</v>
+        <v>"Tuile béton (u)"</v>
       </c>
       <c r="C189" t="str">
         <v>Couverture</v>
@@ -8123,7 +8123,7 @@
       <c r="E189" t="str">
         <v>u</v>
       </c>
-      <c r="F189">
+      <c r="F189" t="str">
         <v>800</v>
       </c>
       <c r="G189" t="str">
@@ -8133,7 +8133,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I189" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J189" t="str">
         <v>2026-10-16</v>
@@ -8145,7 +8145,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M189" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -8153,7 +8153,7 @@
         <v>COUV-04</v>
       </c>
       <c r="B190" t="str">
-        <v>Charpente métallique (kg)</v>
+        <v>"Charpente métallique (kg)"</v>
       </c>
       <c r="C190" t="str">
         <v>Couverture</v>
@@ -8164,7 +8164,7 @@
       <c r="E190" t="str">
         <v>kg</v>
       </c>
-      <c r="F190">
+      <c r="F190" t="str">
         <v>1200</v>
       </c>
       <c r="G190" t="str">
@@ -8174,7 +8174,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I190" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J190" t="str">
         <v>2026-10-16</v>
@@ -8186,7 +8186,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M190" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -8194,7 +8194,7 @@
         <v>COUV-05</v>
       </c>
       <c r="B191" t="str">
-        <v>Gouttière PVC (ml)</v>
+        <v>"Gouttière PVC (ml)"</v>
       </c>
       <c r="C191" t="str">
         <v>Couverture</v>
@@ -8205,7 +8205,7 @@
       <c r="E191" t="str">
         <v>ml</v>
       </c>
-      <c r="F191">
+      <c r="F191" t="str">
         <v>4500</v>
       </c>
       <c r="G191" t="str">
@@ -8215,7 +8215,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I191" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J191" t="str">
         <v>2026-10-16</v>
@@ -8227,7 +8227,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M191" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -8235,7 +8235,7 @@
         <v>MO-01</v>
       </c>
       <c r="B192" t="str">
-        <v>Maçon (journée)</v>
+        <v>"Maçon (journée)"</v>
       </c>
       <c r="C192" t="str">
         <v>Main-d'œuvre</v>
@@ -8246,7 +8246,7 @@
       <c r="E192" t="str">
         <v>jour</v>
       </c>
-      <c r="F192">
+      <c r="F192" t="str">
         <v>15000</v>
       </c>
       <c r="G192" t="str">
@@ -8256,7 +8256,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I192" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J192" t="str">
         <v>2026-10-16</v>
@@ -8268,7 +8268,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M192" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -8276,7 +8276,7 @@
         <v>MO-02</v>
       </c>
       <c r="B193" t="str">
-        <v>Aide-maçon (journée)</v>
+        <v>"Aide-maçon (journée)"</v>
       </c>
       <c r="C193" t="str">
         <v>Main-d'œuvre</v>
@@ -8287,7 +8287,7 @@
       <c r="E193" t="str">
         <v>jour</v>
       </c>
-      <c r="F193">
+      <c r="F193" t="str">
         <v>8000</v>
       </c>
       <c r="G193" t="str">
@@ -8297,7 +8297,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I193" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J193" t="str">
         <v>2026-10-16</v>
@@ -8309,7 +8309,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M193" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -8317,7 +8317,7 @@
         <v>MO-03</v>
       </c>
       <c r="B194" t="str">
-        <v>Ferrailleur (journée)</v>
+        <v>"Ferrailleur (journée)"</v>
       </c>
       <c r="C194" t="str">
         <v>Main-d'œuvre</v>
@@ -8328,7 +8328,7 @@
       <c r="E194" t="str">
         <v>jour</v>
       </c>
-      <c r="F194">
+      <c r="F194" t="str">
         <v>18000</v>
       </c>
       <c r="G194" t="str">
@@ -8338,7 +8338,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I194" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J194" t="str">
         <v>2026-10-16</v>
@@ -8350,7 +8350,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M194" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -8358,7 +8358,7 @@
         <v>MO-04</v>
       </c>
       <c r="B195" t="str">
-        <v>Coffreur (journée)</v>
+        <v>"Coffreur (journée)"</v>
       </c>
       <c r="C195" t="str">
         <v>Main-d'œuvre</v>
@@ -8369,7 +8369,7 @@
       <c r="E195" t="str">
         <v>jour</v>
       </c>
-      <c r="F195">
+      <c r="F195" t="str">
         <v>18000</v>
       </c>
       <c r="G195" t="str">
@@ -8379,7 +8379,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I195" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J195" t="str">
         <v>2026-10-16</v>
@@ -8391,7 +8391,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M195" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -8399,7 +8399,7 @@
         <v>MO-05</v>
       </c>
       <c r="B196" t="str">
-        <v>Peintre (journée)</v>
+        <v>"Peintre (journée)"</v>
       </c>
       <c r="C196" t="str">
         <v>Main-d'œuvre</v>
@@ -8410,7 +8410,7 @@
       <c r="E196" t="str">
         <v>jour</v>
       </c>
-      <c r="F196">
+      <c r="F196" t="str">
         <v>12000</v>
       </c>
       <c r="G196" t="str">
@@ -8420,7 +8420,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I196" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J196" t="str">
         <v>2026-10-16</v>
@@ -8432,7 +8432,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M196" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -8440,7 +8440,7 @@
         <v>MO-06</v>
       </c>
       <c r="B197" t="str">
-        <v>Carreleur (journée)</v>
+        <v>"Carreleur (journée)"</v>
       </c>
       <c r="C197" t="str">
         <v>Main-d'œuvre</v>
@@ -8451,7 +8451,7 @@
       <c r="E197" t="str">
         <v>jour</v>
       </c>
-      <c r="F197">
+      <c r="F197" t="str">
         <v>15000</v>
       </c>
       <c r="G197" t="str">
@@ -8461,7 +8461,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I197" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J197" t="str">
         <v>2026-10-16</v>
@@ -8473,7 +8473,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M197" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -8481,7 +8481,7 @@
         <v>MO-07</v>
       </c>
       <c r="B198" t="str">
-        <v>Plombier (journée)</v>
+        <v>"Plombier (journée)"</v>
       </c>
       <c r="C198" t="str">
         <v>Main-d'œuvre</v>
@@ -8492,7 +8492,7 @@
       <c r="E198" t="str">
         <v>jour</v>
       </c>
-      <c r="F198">
+      <c r="F198" t="str">
         <v>18000</v>
       </c>
       <c r="G198" t="str">
@@ -8502,7 +8502,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I198" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J198" t="str">
         <v>2026-10-16</v>
@@ -8514,7 +8514,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M198" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -8522,7 +8522,7 @@
         <v>MO-08</v>
       </c>
       <c r="B199" t="str">
-        <v>Électricien (journée)</v>
+        <v>"Électricien (journée)"</v>
       </c>
       <c r="C199" t="str">
         <v>Main-d'œuvre</v>
@@ -8533,7 +8533,7 @@
       <c r="E199" t="str">
         <v>jour</v>
       </c>
-      <c r="F199">
+      <c r="F199" t="str">
         <v>18000</v>
       </c>
       <c r="G199" t="str">
@@ -8543,7 +8543,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I199" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J199" t="str">
         <v>2026-10-16</v>
@@ -8555,7 +8555,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M199" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -8563,7 +8563,7 @@
         <v>MO-09</v>
       </c>
       <c r="B200" t="str">
-        <v>Menuisier (journée)</v>
+        <v>"Menuisier (journée)"</v>
       </c>
       <c r="C200" t="str">
         <v>Main-d'œuvre</v>
@@ -8574,7 +8574,7 @@
       <c r="E200" t="str">
         <v>jour</v>
       </c>
-      <c r="F200">
+      <c r="F200" t="str">
         <v>15000</v>
       </c>
       <c r="G200" t="str">
@@ -8584,7 +8584,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I200" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J200" t="str">
         <v>2026-10-16</v>
@@ -8596,7 +8596,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M200" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -8604,7 +8604,7 @@
         <v>MO-10</v>
       </c>
       <c r="B201" t="str">
-        <v>Chef d'équipe (journée)</v>
+        <v>"Chef d'équipe (journée)"</v>
       </c>
       <c r="C201" t="str">
         <v>Main-d'œuvre</v>
@@ -8615,7 +8615,7 @@
       <c r="E201" t="str">
         <v>jour</v>
       </c>
-      <c r="F201">
+      <c r="F201" t="str">
         <v>25000</v>
       </c>
       <c r="G201" t="str">
@@ -8625,7 +8625,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I201" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J201" t="str">
         <v>2026-10-16</v>
@@ -8637,7 +8637,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M201" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -8645,7 +8645,7 @@
         <v>MB-01</v>
       </c>
       <c r="B202" t="str">
-        <v>Ciment CPA 42,5 (sac 50 kg)</v>
+        <v>"Ciment CPA 42,5 (sac 50 kg)"</v>
       </c>
       <c r="C202" t="str">
         <v>Matériaux de base</v>
@@ -8656,7 +8656,7 @@
       <c r="E202" t="str">
         <v>sac 50 kg</v>
       </c>
-      <c r="F202">
+      <c r="F202" t="str">
         <v>5500</v>
       </c>
       <c r="G202" t="str">
@@ -8666,7 +8666,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I202" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J202" t="str">
         <v>2026-10-16</v>
@@ -8678,7 +8678,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M202" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -8686,7 +8686,7 @@
         <v>MB-02</v>
       </c>
       <c r="B203" t="str">
-        <v>Ciment CPJ 42,5 (sac 50 kg)</v>
+        <v>"Ciment CPJ 42,5 (sac 50 kg)"</v>
       </c>
       <c r="C203" t="str">
         <v>Matériaux de base</v>
@@ -8697,7 +8697,7 @@
       <c r="E203" t="str">
         <v>sac 50 kg</v>
       </c>
-      <c r="F203">
+      <c r="F203" t="str">
         <v>4800</v>
       </c>
       <c r="G203" t="str">
@@ -8707,7 +8707,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I203" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J203" t="str">
         <v>2026-10-16</v>
@@ -8719,7 +8719,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M203" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -8727,7 +8727,7 @@
         <v>MB-03</v>
       </c>
       <c r="B204" t="str">
-        <v>Sable de rivière (m³)</v>
+        <v>"Sable de rivière (m³)"</v>
       </c>
       <c r="C204" t="str">
         <v>Matériaux de base</v>
@@ -8738,7 +8738,7 @@
       <c r="E204" t="str">
         <v>m3</v>
       </c>
-      <c r="F204">
+      <c r="F204" t="str">
         <v>65000</v>
       </c>
       <c r="G204" t="str">
@@ -8748,7 +8748,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I204" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J204" t="str">
         <v>2026-10-16</v>
@@ -8760,7 +8760,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M204" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -8768,7 +8768,7 @@
         <v>MB-04</v>
       </c>
       <c r="B205" t="str">
-        <v>Gravier 5/15 (m³)</v>
+        <v>"Gravier 5/15 (m³)"</v>
       </c>
       <c r="C205" t="str">
         <v>Matériaux de base</v>
@@ -8779,7 +8779,7 @@
       <c r="E205" t="str">
         <v>m3</v>
       </c>
-      <c r="F205">
+      <c r="F205" t="str">
         <v>60000</v>
       </c>
       <c r="G205" t="str">
@@ -8789,7 +8789,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I205" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J205" t="str">
         <v>2026-10-16</v>
@@ -8801,7 +8801,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M205" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -8809,7 +8809,7 @@
         <v>MB-05</v>
       </c>
       <c r="B206" t="str">
-        <v>Gravier 15/25 (m³)</v>
+        <v>"Gravier 15/25 (m³)"</v>
       </c>
       <c r="C206" t="str">
         <v>Matériaux de base</v>
@@ -8820,7 +8820,7 @@
       <c r="E206" t="str">
         <v>m3</v>
       </c>
-      <c r="F206">
+      <c r="F206" t="str">
         <v>58000</v>
       </c>
       <c r="G206" t="str">
@@ -8830,7 +8830,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I206" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J206" t="str">
         <v>2026-10-16</v>
@@ -8842,7 +8842,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M206" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -8850,7 +8850,7 @@
         <v>MB-06</v>
       </c>
       <c r="B207" t="str">
-        <v>Latérite (m³)</v>
+        <v>"Latérite (m³)"</v>
       </c>
       <c r="C207" t="str">
         <v>Matériaux de base</v>
@@ -8861,7 +8861,7 @@
       <c r="E207" t="str">
         <v>m3</v>
       </c>
-      <c r="F207">
+      <c r="F207" t="str">
         <v>40000</v>
       </c>
       <c r="G207" t="str">
@@ -8871,7 +8871,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I207" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J207" t="str">
         <v>2026-10-16</v>
@@ -8883,7 +8883,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M207" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -8891,7 +8891,7 @@
         <v>MB-07</v>
       </c>
       <c r="B208" t="str">
-        <v>Argile (m³)</v>
+        <v>"Argile (m³)"</v>
       </c>
       <c r="C208" t="str">
         <v>Matériaux de base</v>
@@ -8902,7 +8902,7 @@
       <c r="E208" t="str">
         <v>m3</v>
       </c>
-      <c r="F208">
+      <c r="F208" t="str">
         <v>25000</v>
       </c>
       <c r="G208" t="str">
@@ -8912,7 +8912,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I208" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J208" t="str">
         <v>2026-10-16</v>
@@ -8924,7 +8924,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M208" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -8932,7 +8932,7 @@
         <v>MB-08</v>
       </c>
       <c r="B209" t="str">
-        <v>Eau (m³)</v>
+        <v>"Eau (m³)"</v>
       </c>
       <c r="C209" t="str">
         <v>Matériaux de base</v>
@@ -8943,7 +8943,7 @@
       <c r="E209" t="str">
         <v>m3</v>
       </c>
-      <c r="F209">
+      <c r="F209" t="str">
         <v>1500</v>
       </c>
       <c r="G209" t="str">
@@ -8953,7 +8953,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I209" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J209" t="str">
         <v>2026-10-16</v>
@@ -8965,7 +8965,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M209" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -8973,7 +8973,7 @@
         <v>MB-09</v>
       </c>
       <c r="B210" t="str">
-        <v>Additif béton (kg)</v>
+        <v>"Additif béton (kg)"</v>
       </c>
       <c r="C210" t="str">
         <v>Matériaux de base</v>
@@ -8984,7 +8984,7 @@
       <c r="E210" t="str">
         <v>kg</v>
       </c>
-      <c r="F210">
+      <c r="F210" t="str">
         <v>2500</v>
       </c>
       <c r="G210" t="str">
@@ -8994,7 +8994,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I210" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J210" t="str">
         <v>2026-10-16</v>
@@ -9006,7 +9006,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M210" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -9014,7 +9014,7 @@
         <v>MB-10</v>
       </c>
       <c r="B211" t="str">
-        <v>Treillis soudé (m²)</v>
+        <v>"Treillis soudé (m²)"</v>
       </c>
       <c r="C211" t="str">
         <v>Matériaux de base</v>
@@ -9025,7 +9025,7 @@
       <c r="E211" t="str">
         <v>m2</v>
       </c>
-      <c r="F211">
+      <c r="F211" t="str">
         <v>4500</v>
       </c>
       <c r="G211" t="str">
@@ -9035,7 +9035,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I211" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J211" t="str">
         <v>2026-10-16</v>
@@ -9047,7 +9047,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M211" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -9055,7 +9055,7 @@
         <v>MB-11</v>
       </c>
       <c r="B212" t="str">
-        <v>Barre acier HA (kg)</v>
+        <v>"Barre acier HA (kg)"</v>
       </c>
       <c r="C212" t="str">
         <v>Matériaux de base</v>
@@ -9066,7 +9066,7 @@
       <c r="E212" t="str">
         <v>kg</v>
       </c>
-      <c r="F212">
+      <c r="F212" t="str">
         <v>3500</v>
       </c>
       <c r="G212" t="str">
@@ -9076,7 +9076,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I212" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J212" t="str">
         <v>2026-10-16</v>
@@ -9088,7 +9088,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M212" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -9096,7 +9096,7 @@
         <v>MB-12</v>
       </c>
       <c r="B213" t="str">
-        <v>Fil d'attache (kg)</v>
+        <v>"Fil d'attache (kg)"</v>
       </c>
       <c r="C213" t="str">
         <v>Matériaux de base</v>
@@ -9107,7 +9107,7 @@
       <c r="E213" t="str">
         <v>kg</v>
       </c>
-      <c r="F213">
+      <c r="F213" t="str">
         <v>1200</v>
       </c>
       <c r="G213" t="str">
@@ -9117,7 +9117,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I213" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J213" t="str">
         <v>2026-10-16</v>
@@ -9129,7 +9129,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M213" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -9137,7 +9137,7 @@
         <v>MB-13</v>
       </c>
       <c r="B214" t="str">
-        <v>Clous (kg)</v>
+        <v>"Clous (kg)"</v>
       </c>
       <c r="C214" t="str">
         <v>Matériaux de base</v>
@@ -9148,7 +9148,7 @@
       <c r="E214" t="str">
         <v>kg</v>
       </c>
-      <c r="F214">
+      <c r="F214" t="str">
         <v>1800</v>
       </c>
       <c r="G214" t="str">
@@ -9158,7 +9158,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I214" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J214" t="str">
         <v>2026-10-16</v>
@@ -9170,7 +9170,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M214" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -9178,7 +9178,7 @@
         <v>MB-14</v>
       </c>
       <c r="B215" t="str">
-        <v>Vis (kg)</v>
+        <v>"Vis (kg)"</v>
       </c>
       <c r="C215" t="str">
         <v>Matériaux de base</v>
@@ -9189,7 +9189,7 @@
       <c r="E215" t="str">
         <v>kg</v>
       </c>
-      <c r="F215">
+      <c r="F215" t="str">
         <v>3000</v>
       </c>
       <c r="G215" t="str">
@@ -9199,7 +9199,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I215" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J215" t="str">
         <v>2026-10-16</v>
@@ -9211,7 +9211,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M215" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="216">
@@ -9219,7 +9219,7 @@
         <v>MB-15</v>
       </c>
       <c r="B216" t="str">
-        <v>Mortier prêt à l'emploi (m³)</v>
+        <v>"Mortier prêt à l'emploi (m³)"</v>
       </c>
       <c r="C216" t="str">
         <v>Matériaux de base</v>
@@ -9230,7 +9230,7 @@
       <c r="E216" t="str">
         <v>m3</v>
       </c>
-      <c r="F216">
+      <c r="F216" t="str">
         <v>95000</v>
       </c>
       <c r="G216" t="str">
@@ -9240,7 +9240,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I216" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J216" t="str">
         <v>2026-10-16</v>
@@ -9252,7 +9252,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M216" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="217">
@@ -9260,7 +9260,7 @@
         <v>MB-16</v>
       </c>
       <c r="B217" t="str">
-        <v>Enduit de façade (m²)</v>
+        <v>"Enduit de façade (m²)"</v>
       </c>
       <c r="C217" t="str">
         <v>Matériaux de base</v>
@@ -9271,7 +9271,7 @@
       <c r="E217" t="str">
         <v>m2</v>
       </c>
-      <c r="F217">
+      <c r="F217" t="str">
         <v>3500</v>
       </c>
       <c r="G217" t="str">
@@ -9281,7 +9281,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I217" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J217" t="str">
         <v>2026-10-16</v>
@@ -9293,7 +9293,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M217" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -9301,7 +9301,7 @@
         <v>MB-17</v>
       </c>
       <c r="B218" t="str">
-        <v>Peinture (L)</v>
+        <v>"Peinture (L)"</v>
       </c>
       <c r="C218" t="str">
         <v>Matériaux de base</v>
@@ -9312,7 +9312,7 @@
       <c r="E218" t="str">
         <v>L</v>
       </c>
-      <c r="F218">
+      <c r="F218" t="str">
         <v>4500</v>
       </c>
       <c r="G218" t="str">
@@ -9322,7 +9322,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I218" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J218" t="str">
         <v>2026-10-16</v>
@@ -9334,7 +9334,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M218" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -9342,7 +9342,7 @@
         <v>MENU-01</v>
       </c>
       <c r="B219" t="str">
-        <v>Porte bois pleine (u)</v>
+        <v>"Porte bois pleine (u)"</v>
       </c>
       <c r="C219" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9353,7 +9353,7 @@
       <c r="E219" t="str">
         <v>u</v>
       </c>
-      <c r="F219">
+      <c r="F219" t="str">
         <v>120000</v>
       </c>
       <c r="G219" t="str">
@@ -9363,7 +9363,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I219" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J219" t="str">
         <v>2026-10-16</v>
@@ -9375,7 +9375,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M219" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -9383,7 +9383,7 @@
         <v>MENU-02</v>
       </c>
       <c r="B220" t="str">
-        <v>Fenêtre bois (u)</v>
+        <v>"Fenêtre bois (u)"</v>
       </c>
       <c r="C220" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9394,7 +9394,7 @@
       <c r="E220" t="str">
         <v>u</v>
       </c>
-      <c r="F220">
+      <c r="F220" t="str">
         <v>95000</v>
       </c>
       <c r="G220" t="str">
@@ -9404,7 +9404,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I220" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J220" t="str">
         <v>2026-10-16</v>
@@ -9416,7 +9416,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M220" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -9424,7 +9424,7 @@
         <v>MENU-03</v>
       </c>
       <c r="B221" t="str">
-        <v>Porte métallique (u)</v>
+        <v>"Porte métallique (u)"</v>
       </c>
       <c r="C221" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9435,7 +9435,7 @@
       <c r="E221" t="str">
         <v>u</v>
       </c>
-      <c r="F221">
+      <c r="F221" t="str">
         <v>180000</v>
       </c>
       <c r="G221" t="str">
@@ -9445,7 +9445,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I221" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J221" t="str">
         <v>2026-10-16</v>
@@ -9457,7 +9457,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M221" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -9465,7 +9465,7 @@
         <v>MENU-04</v>
       </c>
       <c r="B222" t="str">
-        <v>Fenêtre aluminium (u)</v>
+        <v>"Fenêtre aluminium (u)"</v>
       </c>
       <c r="C222" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9476,7 +9476,7 @@
       <c r="E222" t="str">
         <v>u</v>
       </c>
-      <c r="F222">
+      <c r="F222" t="str">
         <v>110000</v>
       </c>
       <c r="G222" t="str">
@@ -9486,7 +9486,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I222" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J222" t="str">
         <v>2026-10-16</v>
@@ -9498,7 +9498,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M222" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -9506,7 +9506,7 @@
         <v>MENU-05</v>
       </c>
       <c r="B223" t="str">
-        <v>Placard / armoire (m²)</v>
+        <v>"Placard / armoire (m²)"</v>
       </c>
       <c r="C223" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9517,7 +9517,7 @@
       <c r="E223" t="str">
         <v>m2</v>
       </c>
-      <c r="F223">
+      <c r="F223" t="str">
         <v>45000</v>
       </c>
       <c r="G223" t="str">
@@ -9527,7 +9527,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I223" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J223" t="str">
         <v>2026-10-16</v>
@@ -9539,7 +9539,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M223" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -9547,7 +9547,7 @@
         <v>MENU-06</v>
       </c>
       <c r="B224" t="str">
-        <v>Plinthe (ml)</v>
+        <v>"Plinthe (ml)"</v>
       </c>
       <c r="C224" t="str">
         <v>Menuiserie et fermeture</v>
@@ -9558,7 +9558,7 @@
       <c r="E224" t="str">
         <v>ml</v>
       </c>
-      <c r="F224">
+      <c r="F224" t="str">
         <v>3500</v>
       </c>
       <c r="G224" t="str">
@@ -9568,7 +9568,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I224" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J224" t="str">
         <v>2026-10-16</v>
@@ -9580,7 +9580,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M224" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -9588,7 +9588,7 @@
         <v>PLO-01</v>
       </c>
       <c r="B225" t="str">
-        <v>Tube PVC Ø100 (ml)</v>
+        <v>"Tube PVC Ø100 (ml)"</v>
       </c>
       <c r="C225" t="str">
         <v>Plomberie et assainissement</v>
@@ -9599,7 +9599,7 @@
       <c r="E225" t="str">
         <v>ml</v>
       </c>
-      <c r="F225">
+      <c r="F225" t="str">
         <v>3500</v>
       </c>
       <c r="G225" t="str">
@@ -9609,7 +9609,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I225" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J225" t="str">
         <v>2026-10-16</v>
@@ -9621,7 +9621,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M225" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -9629,7 +9629,7 @@
         <v>PLO-02</v>
       </c>
       <c r="B226" t="str">
-        <v>Coude PVC (u)</v>
+        <v>"Coude PVC (u)"</v>
       </c>
       <c r="C226" t="str">
         <v>Plomberie et assainissement</v>
@@ -9640,7 +9640,7 @@
       <c r="E226" t="str">
         <v>u</v>
       </c>
-      <c r="F226">
+      <c r="F226" t="str">
         <v>1200</v>
       </c>
       <c r="G226" t="str">
@@ -9650,7 +9650,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I226" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J226" t="str">
         <v>2026-10-16</v>
@@ -9662,7 +9662,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M226" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -9670,7 +9670,7 @@
         <v>PLO-03</v>
       </c>
       <c r="B227" t="str">
-        <v>Té PVC (u)</v>
+        <v>"Té PVC (u)"</v>
       </c>
       <c r="C227" t="str">
         <v>Plomberie et assainissement</v>
@@ -9681,7 +9681,7 @@
       <c r="E227" t="str">
         <v>u</v>
       </c>
-      <c r="F227">
+      <c r="F227" t="str">
         <v>1500</v>
       </c>
       <c r="G227" t="str">
@@ -9691,7 +9691,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I227" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J227" t="str">
         <v>2026-10-16</v>
@@ -9703,7 +9703,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M227" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -9711,7 +9711,7 @@
         <v>PLO-04</v>
       </c>
       <c r="B228" t="str">
-        <v>Vanne à boisseau (u)</v>
+        <v>"Vanne à boisseau (u)"</v>
       </c>
       <c r="C228" t="str">
         <v>Plomberie et assainissement</v>
@@ -9722,7 +9722,7 @@
       <c r="E228" t="str">
         <v>u</v>
       </c>
-      <c r="F228">
+      <c r="F228" t="str">
         <v>8000</v>
       </c>
       <c r="G228" t="str">
@@ -9732,7 +9732,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I228" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J228" t="str">
         <v>2026-10-16</v>
@@ -9744,7 +9744,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M228" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -9752,7 +9752,7 @@
         <v>PLO-05</v>
       </c>
       <c r="B229" t="str">
-        <v>Robinet (u)</v>
+        <v>"Robinet (u)"</v>
       </c>
       <c r="C229" t="str">
         <v>Plomberie et assainissement</v>
@@ -9763,7 +9763,7 @@
       <c r="E229" t="str">
         <v>u</v>
       </c>
-      <c r="F229">
+      <c r="F229" t="str">
         <v>6000</v>
       </c>
       <c r="G229" t="str">
@@ -9773,7 +9773,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I229" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J229" t="str">
         <v>2026-10-16</v>
@@ -9785,7 +9785,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M229" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -9793,7 +9793,7 @@
         <v>PLO-06</v>
       </c>
       <c r="B230" t="str">
-        <v>WC complet (u)</v>
+        <v>"WC complet (u)"</v>
       </c>
       <c r="C230" t="str">
         <v>Plomberie et assainissement</v>
@@ -9804,7 +9804,7 @@
       <c r="E230" t="str">
         <v>u</v>
       </c>
-      <c r="F230">
+      <c r="F230" t="str">
         <v>45000</v>
       </c>
       <c r="G230" t="str">
@@ -9814,7 +9814,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I230" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J230" t="str">
         <v>2026-10-16</v>
@@ -9826,7 +9826,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M230" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -9834,7 +9834,7 @@
         <v>PLO-07</v>
       </c>
       <c r="B231" t="str">
-        <v>Lavabo (u)</v>
+        <v>"Lavabo (u)"</v>
       </c>
       <c r="C231" t="str">
         <v>Plomberie et assainissement</v>
@@ -9845,7 +9845,7 @@
       <c r="E231" t="str">
         <v>u</v>
       </c>
-      <c r="F231">
+      <c r="F231" t="str">
         <v>35000</v>
       </c>
       <c r="G231" t="str">
@@ -9855,7 +9855,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I231" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J231" t="str">
         <v>2026-10-16</v>
@@ -9867,7 +9867,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M231" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -9875,7 +9875,7 @@
         <v>PLO-08</v>
       </c>
       <c r="B232" t="str">
-        <v>Douche (u)</v>
+        <v>"Douche (u)"</v>
       </c>
       <c r="C232" t="str">
         <v>Plomberie et assainissement</v>
@@ -9886,7 +9886,7 @@
       <c r="E232" t="str">
         <v>u</v>
       </c>
-      <c r="F232">
+      <c r="F232" t="str">
         <v>40000</v>
       </c>
       <c r="G232" t="str">
@@ -9896,7 +9896,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I232" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J232" t="str">
         <v>2026-10-16</v>
@@ -9908,7 +9908,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M232" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -9916,7 +9916,7 @@
         <v>PLO-09</v>
       </c>
       <c r="B233" t="str">
-        <v>Chauffe-eau (u)</v>
+        <v>"Chauffe-eau (u)"</v>
       </c>
       <c r="C233" t="str">
         <v>Plomberie et assainissement</v>
@@ -9927,7 +9927,7 @@
       <c r="E233" t="str">
         <v>u</v>
       </c>
-      <c r="F233">
+      <c r="F233" t="str">
         <v>120000</v>
       </c>
       <c r="G233" t="str">
@@ -9937,7 +9937,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I233" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J233" t="str">
         <v>2026-10-16</v>
@@ -9949,7 +9949,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M233" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -9957,7 +9957,7 @@
         <v>PLO-10</v>
       </c>
       <c r="B234" t="str">
-        <v>Fosse septique (u)</v>
+        <v>"Fosse septique (u)"</v>
       </c>
       <c r="C234" t="str">
         <v>Plomberie et assainissement</v>
@@ -9968,7 +9968,7 @@
       <c r="E234" t="str">
         <v>u</v>
       </c>
-      <c r="F234">
+      <c r="F234" t="str">
         <v>250000</v>
       </c>
       <c r="G234" t="str">
@@ -9978,7 +9978,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I234" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J234" t="str">
         <v>2026-10-16</v>
@@ -9990,7 +9990,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M234" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -9998,7 +9998,7 @@
         <v>PLO-11</v>
       </c>
       <c r="B235" t="str">
-        <v>Regard béton (u)</v>
+        <v>"Regard béton (u)"</v>
       </c>
       <c r="C235" t="str">
         <v>Plomberie et assainissement</v>
@@ -10009,7 +10009,7 @@
       <c r="E235" t="str">
         <v>u</v>
       </c>
-      <c r="F235">
+      <c r="F235" t="str">
         <v>35000</v>
       </c>
       <c r="G235" t="str">
@@ -10019,7 +10019,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I235" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J235" t="str">
         <v>2026-10-16</v>
@@ -10031,7 +10031,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M235" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -10039,7 +10039,7 @@
         <v>PLO-12</v>
       </c>
       <c r="B236" t="str">
-        <v>Canalisation (ml)</v>
+        <v>"Canalisation (ml)"</v>
       </c>
       <c r="C236" t="str">
         <v>Plomberie et assainissement</v>
@@ -10050,7 +10050,7 @@
       <c r="E236" t="str">
         <v>ml</v>
       </c>
-      <c r="F236">
+      <c r="F236" t="str">
         <v>8000</v>
       </c>
       <c r="G236" t="str">
@@ -10060,7 +10060,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I236" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J236" t="str">
         <v>2026-10-16</v>
@@ -10072,7 +10072,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M236" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -10080,7 +10080,7 @@
         <v>PLO-13</v>
       </c>
       <c r="B237" t="str">
-        <v>Pompage / essai (forfait)</v>
+        <v>"Pompage / essai (forfait)"</v>
       </c>
       <c r="C237" t="str">
         <v>Plomberie et assainissement</v>
@@ -10091,7 +10091,7 @@
       <c r="E237" t="str">
         <v>forfait</v>
       </c>
-      <c r="F237">
+      <c r="F237" t="str">
         <v>60000</v>
       </c>
       <c r="G237" t="str">
@@ -10101,7 +10101,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I237" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J237" t="str">
         <v>2026-10-16</v>
@@ -10113,7 +10113,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M237" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -10121,7 +10121,7 @@
         <v>TRA-01</v>
       </c>
       <c r="B238" t="str">
-        <v>Transport matériaux (voyage camion)</v>
+        <v>"Transport matériaux (voyage camion)"</v>
       </c>
       <c r="C238" t="str">
         <v>Transport</v>
@@ -10132,7 +10132,7 @@
       <c r="E238" t="str">
         <v>voyage</v>
       </c>
-      <c r="F238">
+      <c r="F238" t="str">
         <v>150000</v>
       </c>
       <c r="G238" t="str">
@@ -10142,7 +10142,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I238" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J238" t="str">
         <v>2026-10-16</v>
@@ -10154,7 +10154,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M238" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -10162,7 +10162,7 @@
         <v>TRA-02</v>
       </c>
       <c r="B239" t="str">
-        <v>Location camion (jour)</v>
+        <v>"Location camion (jour)"</v>
       </c>
       <c r="C239" t="str">
         <v>Transport</v>
@@ -10173,7 +10173,7 @@
       <c r="E239" t="str">
         <v>jour</v>
       </c>
-      <c r="F239">
+      <c r="F239" t="str">
         <v>350000</v>
       </c>
       <c r="G239" t="str">
@@ -10183,7 +10183,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I239" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J239" t="str">
         <v>2026-10-16</v>
@@ -10195,7 +10195,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M239" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -10203,7 +10203,7 @@
         <v>TRA-03</v>
       </c>
       <c r="B240" t="str">
-        <v>Carburant (L)</v>
+        <v>"Carburant (L)"</v>
       </c>
       <c r="C240" t="str">
         <v>Transport</v>
@@ -10214,7 +10214,7 @@
       <c r="E240" t="str">
         <v>L</v>
       </c>
-      <c r="F240">
+      <c r="F240" t="str">
         <v>650</v>
       </c>
       <c r="G240" t="str">
@@ -10224,7 +10224,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I240" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J240" t="str">
         <v>2026-10-16</v>
@@ -10236,7 +10236,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M240" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -10244,7 +10244,7 @@
         <v>TRA-04</v>
       </c>
       <c r="B241" t="str">
-        <v>Manutention (forfait)</v>
+        <v>"Manutention (forfait)"</v>
       </c>
       <c r="C241" t="str">
         <v>Transport</v>
@@ -10255,7 +10255,7 @@
       <c r="E241" t="str">
         <v>forfait</v>
       </c>
-      <c r="F241">
+      <c r="F241" t="str">
         <v>45000</v>
       </c>
       <c r="G241" t="str">
@@ -10265,7 +10265,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I241" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J241" t="str">
         <v>2026-10-16</v>
@@ -10277,7 +10277,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M241" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -10285,7 +10285,7 @@
         <v>ELEC-01</v>
       </c>
       <c r="B242" t="str">
-        <v>Câble électrique (ml)</v>
+        <v>"Câble électrique (ml)"</v>
       </c>
       <c r="C242" t="str">
         <v>Électricité</v>
@@ -10296,7 +10296,7 @@
       <c r="E242" t="str">
         <v>ml</v>
       </c>
-      <c r="F242">
+      <c r="F242" t="str">
         <v>1200</v>
       </c>
       <c r="G242" t="str">
@@ -10306,7 +10306,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I242" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J242" t="str">
         <v>2026-10-16</v>
@@ -10318,7 +10318,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M242" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -10326,7 +10326,7 @@
         <v>ELEC-02</v>
       </c>
       <c r="B243" t="str">
-        <v>Disjoncteur (u)</v>
+        <v>"Disjoncteur (u)"</v>
       </c>
       <c r="C243" t="str">
         <v>Électricité</v>
@@ -10337,7 +10337,7 @@
       <c r="E243" t="str">
         <v>u</v>
       </c>
-      <c r="F243">
+      <c r="F243" t="str">
         <v>8000</v>
       </c>
       <c r="G243" t="str">
@@ -10347,7 +10347,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I243" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J243" t="str">
         <v>2026-10-16</v>
@@ -10359,7 +10359,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M243" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -10367,7 +10367,7 @@
         <v>ELEC-03</v>
       </c>
       <c r="B244" t="str">
-        <v>Tableau électrique (u)</v>
+        <v>"Tableau électrique (u)"</v>
       </c>
       <c r="C244" t="str">
         <v>Électricité</v>
@@ -10378,7 +10378,7 @@
       <c r="E244" t="str">
         <v>u</v>
       </c>
-      <c r="F244">
+      <c r="F244" t="str">
         <v>65000</v>
       </c>
       <c r="G244" t="str">
@@ -10388,7 +10388,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I244" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J244" t="str">
         <v>2026-10-16</v>
@@ -10400,7 +10400,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M244" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -10408,7 +10408,7 @@
         <v>ELEC-04</v>
       </c>
       <c r="B245" t="str">
-        <v>Prise (u)</v>
+        <v>"Prise (u)"</v>
       </c>
       <c r="C245" t="str">
         <v>Électricité</v>
@@ -10419,7 +10419,7 @@
       <c r="E245" t="str">
         <v>u</v>
       </c>
-      <c r="F245">
+      <c r="F245" t="str">
         <v>3500</v>
       </c>
       <c r="G245" t="str">
@@ -10429,7 +10429,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I245" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J245" t="str">
         <v>2026-10-16</v>
@@ -10441,7 +10441,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M245" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -10449,7 +10449,7 @@
         <v>ELEC-05</v>
       </c>
       <c r="B246" t="str">
-        <v>Interrupteur (u)</v>
+        <v>"Interrupteur (u)"</v>
       </c>
       <c r="C246" t="str">
         <v>Électricité</v>
@@ -10460,7 +10460,7 @@
       <c r="E246" t="str">
         <v>u</v>
       </c>
-      <c r="F246">
+      <c r="F246" t="str">
         <v>3000</v>
       </c>
       <c r="G246" t="str">
@@ -10470,7 +10470,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I246" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J246" t="str">
         <v>2026-10-16</v>
@@ -10482,7 +10482,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M246" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -10490,7 +10490,7 @@
         <v>ELEC-06</v>
       </c>
       <c r="B247" t="str">
-        <v>Luminaire (u)</v>
+        <v>"Luminaire (u)"</v>
       </c>
       <c r="C247" t="str">
         <v>Électricité</v>
@@ -10501,7 +10501,7 @@
       <c r="E247" t="str">
         <v>u</v>
       </c>
-      <c r="F247">
+      <c r="F247" t="str">
         <v>15000</v>
       </c>
       <c r="G247" t="str">
@@ -10511,7 +10511,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I247" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J247" t="str">
         <v>2026-10-16</v>
@@ -10523,7 +10523,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M247" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -10531,7 +10531,7 @@
         <v>ELEC-07</v>
       </c>
       <c r="B248" t="str">
-        <v>Gaine (ml)</v>
+        <v>"Gaine (ml)"</v>
       </c>
       <c r="C248" t="str">
         <v>Électricité</v>
@@ -10542,7 +10542,7 @@
       <c r="E248" t="str">
         <v>ml</v>
       </c>
-      <c r="F248">
+      <c r="F248" t="str">
         <v>400</v>
       </c>
       <c r="G248" t="str">
@@ -10552,7 +10552,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I248" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J248" t="str">
         <v>2026-10-16</v>
@@ -10564,7 +10564,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M248" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -10572,7 +10572,7 @@
         <v>ELEC-08</v>
       </c>
       <c r="B249" t="str">
-        <v>Mise à la terre (forfait)</v>
+        <v>"Mise à la terre (forfait)"</v>
       </c>
       <c r="C249" t="str">
         <v>Électricité</v>
@@ -10583,7 +10583,7 @@
       <c r="E249" t="str">
         <v>forfait</v>
       </c>
-      <c r="F249">
+      <c r="F249" t="str">
         <v>80000</v>
       </c>
       <c r="G249" t="str">
@@ -10593,7 +10593,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I249" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J249" t="str">
         <v>2026-10-16</v>
@@ -10605,7 +10605,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M249" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="250">
@@ -10613,7 +10613,7 @@
         <v>ELEC-09</v>
       </c>
       <c r="B250" t="str">
-        <v>Groupe électrogène (jour)</v>
+        <v>"Groupe électrogène (jour)"</v>
       </c>
       <c r="C250" t="str">
         <v>Électricité</v>
@@ -10624,7 +10624,7 @@
       <c r="E250" t="str">
         <v>jour</v>
       </c>
-      <c r="F250">
+      <c r="F250" t="str">
         <v>75000</v>
       </c>
       <c r="G250" t="str">
@@ -10634,7 +10634,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I250" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J250" t="str">
         <v>2026-10-16</v>
@@ -10646,7 +10646,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M250" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -10654,7 +10654,7 @@
         <v>ELEC-10</v>
       </c>
       <c r="B251" t="str">
-        <v>Installation électrique (m²)</v>
+        <v>"Installation électrique (m²)"</v>
       </c>
       <c r="C251" t="str">
         <v>Électricité</v>
@@ -10665,7 +10665,7 @@
       <c r="E251" t="str">
         <v>m2</v>
       </c>
-      <c r="F251">
+      <c r="F251" t="str">
         <v>12000</v>
       </c>
       <c r="G251" t="str">
@@ -10675,7 +10675,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I251" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J251" t="str">
         <v>2026-10-16</v>
@@ -10687,7 +10687,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M251" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="252">
@@ -10695,7 +10695,7 @@
         <v>ELEC-11</v>
       </c>
       <c r="B252" t="str">
-        <v>Armoire électrique (u)</v>
+        <v>"Armoire électrique (u)"</v>
       </c>
       <c r="C252" t="str">
         <v>Électricité</v>
@@ -10706,7 +10706,7 @@
       <c r="E252" t="str">
         <v>u</v>
       </c>
-      <c r="F252">
+      <c r="F252" t="str">
         <v>95000</v>
       </c>
       <c r="G252" t="str">
@@ -10716,7 +10716,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I252" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J252" t="str">
         <v>2026-10-16</v>
@@ -10728,7 +10728,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M252" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -10736,7 +10736,7 @@
         <v>ELEC-12</v>
       </c>
       <c r="B253" t="str">
-        <v>Paratonnerre (u)</v>
+        <v>"Paratonnerre (u)"</v>
       </c>
       <c r="C253" t="str">
         <v>Électricité</v>
@@ -10747,7 +10747,7 @@
       <c r="E253" t="str">
         <v>u</v>
       </c>
-      <c r="F253">
+      <c r="F253" t="str">
         <v>250000</v>
       </c>
       <c r="G253" t="str">
@@ -10757,7 +10757,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I253" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J253" t="str">
         <v>2026-10-16</v>
@@ -10769,7 +10769,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M253" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="254">
@@ -10777,7 +10777,7 @@
         <v>EPI-01</v>
       </c>
       <c r="B254" t="str">
-        <v>Casque de chantier (u)</v>
+        <v>"Casque de chantier (u)"</v>
       </c>
       <c r="C254" t="str">
         <v>Équipement de sécurité</v>
@@ -10788,7 +10788,7 @@
       <c r="E254" t="str">
         <v>u</v>
       </c>
-      <c r="F254">
+      <c r="F254" t="str">
         <v>8000</v>
       </c>
       <c r="G254" t="str">
@@ -10798,7 +10798,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I254" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J254" t="str">
         <v>2026-10-16</v>
@@ -10810,7 +10810,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M254" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="255">
@@ -10818,7 +10818,7 @@
         <v>EPI-02</v>
       </c>
       <c r="B255" t="str">
-        <v>Gants de protection (paire)</v>
+        <v>"Gants de protection (paire)"</v>
       </c>
       <c r="C255" t="str">
         <v>Équipement de sécurité</v>
@@ -10829,7 +10829,7 @@
       <c r="E255" t="str">
         <v>paire</v>
       </c>
-      <c r="F255">
+      <c r="F255" t="str">
         <v>2500</v>
       </c>
       <c r="G255" t="str">
@@ -10839,7 +10839,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I255" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J255" t="str">
         <v>2026-10-16</v>
@@ -10851,7 +10851,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M255" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="256">
@@ -10859,7 +10859,7 @@
         <v>EPI-03</v>
       </c>
       <c r="B256" t="str">
-        <v>Chaussures de sécurité (paire)</v>
+        <v>"Chaussures de sécurité (paire)"</v>
       </c>
       <c r="C256" t="str">
         <v>Équipement de sécurité</v>
@@ -10870,7 +10870,7 @@
       <c r="E256" t="str">
         <v>paire</v>
       </c>
-      <c r="F256">
+      <c r="F256" t="str">
         <v>25000</v>
       </c>
       <c r="G256" t="str">
@@ -10880,7 +10880,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I256" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J256" t="str">
         <v>2026-10-16</v>
@@ -10892,7 +10892,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M256" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="257">
@@ -10900,7 +10900,7 @@
         <v>EPI-04</v>
       </c>
       <c r="B257" t="str">
-        <v>Gilet haute visibilité (u)</v>
+        <v>"Gilet haute visibilité (u)"</v>
       </c>
       <c r="C257" t="str">
         <v>Équipement de sécurité</v>
@@ -10911,7 +10911,7 @@
       <c r="E257" t="str">
         <v>u</v>
       </c>
-      <c r="F257">
+      <c r="F257" t="str">
         <v>3000</v>
       </c>
       <c r="G257" t="str">
@@ -10921,7 +10921,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I257" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J257" t="str">
         <v>2026-10-16</v>
@@ -10933,7 +10933,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M257" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="258">
@@ -10941,7 +10941,7 @@
         <v>EPI-05</v>
       </c>
       <c r="B258" t="str">
-        <v>Lunettes de protection (u)</v>
+        <v>"Lunettes de protection (u)"</v>
       </c>
       <c r="C258" t="str">
         <v>Équipement de sécurité</v>
@@ -10952,7 +10952,7 @@
       <c r="E258" t="str">
         <v>u</v>
       </c>
-      <c r="F258">
+      <c r="F258" t="str">
         <v>4000</v>
       </c>
       <c r="G258" t="str">
@@ -10962,7 +10962,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I258" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J258" t="str">
         <v>2026-10-16</v>
@@ -10974,7 +10974,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M258" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="259">
@@ -10982,7 +10982,7 @@
         <v>EPI-06</v>
       </c>
       <c r="B259" t="str">
-        <v>Harnais de sécurité (u)</v>
+        <v>"Harnais de sécurité (u)"</v>
       </c>
       <c r="C259" t="str">
         <v>Équipement de sécurité</v>
@@ -10993,7 +10993,7 @@
       <c r="E259" t="str">
         <v>u</v>
       </c>
-      <c r="F259">
+      <c r="F259" t="str">
         <v>35000</v>
       </c>
       <c r="G259" t="str">
@@ -11003,7 +11003,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I259" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J259" t="str">
         <v>2026-10-16</v>
@@ -11015,7 +11015,7 @@
         <v>a_verifier</v>
       </c>
       <c r="M259" t="str">
-        <v>Prix estimé à confirmer</v>
+        <v/>
       </c>
     </row>
     <row r="260">
@@ -11023,7 +11023,7 @@
         <v>EPI-07</v>
       </c>
       <c r="B260" t="str">
-        <v>Extincteur (u)</v>
+        <v>"Extincteur (u)"</v>
       </c>
       <c r="C260" t="str">
         <v>Équipement de sécurité</v>
@@ -11034,7 +11034,7 @@
       <c r="E260" t="str">
         <v>u</v>
       </c>
-      <c r="F260">
+      <c r="F260" t="str">
         <v>25000</v>
       </c>
       <c r="G260" t="str">
@@ -11044,7 +11044,7 @@
         <v>Marché ivoirien</v>
       </c>
       <c r="I260" t="str">
-        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+        <v>"Marché ivoirien 2026 (estimation) - à vérifier"</v>
       </c>
       <c r="J260" t="str">
         <v>2026-10-16</v>
@@ -11056,12 +11056,832 @@
         <v>a_verifier</v>
       </c>
       <c r="M260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>ACI-12</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Bloc agglomere (u)</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Maçonnerie</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Agglos</v>
+      </c>
+      <c r="E261" t="str">
+        <v>u</v>
+      </c>
+      <c r="F261">
+        <v>15000</v>
+      </c>
+      <c r="G261" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H261" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I261" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J261" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K261" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L261" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M261" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>BET-99</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Betonne (concrete) (m3)</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Béton</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Béton prêt</v>
+      </c>
+      <c r="E262" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F262">
+        <v>87000</v>
+      </c>
+      <c r="G262" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H262" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I262" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J262" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K262" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L262" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M262" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>LTR-01</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Laterite (m3)</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Matériaux de base</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Sols</v>
+      </c>
+      <c r="E263" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F263">
+        <v>40000</v>
+      </c>
+      <c r="G263" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H263" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J263" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K263" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L263" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M263" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>GRN-01</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Granulat (m3)</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Matériaux de base</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Granulats</v>
+      </c>
+      <c r="E264" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F264">
+        <v>55000</v>
+      </c>
+      <c r="G264" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H264" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I264" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J264" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K264" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L264" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M264" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TER-99</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Terrassement (m3)</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Terrassement</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Terrassement</v>
+      </c>
+      <c r="E265" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F265">
+        <v>45000</v>
+      </c>
+      <c r="G265" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H265" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I265" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J265" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K265" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L265" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M265" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>EXC-01</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Excavation (m3)</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Terrassement</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Excavation</v>
+      </c>
+      <c r="E266" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F266">
+        <v>50000</v>
+      </c>
+      <c r="G266" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H266" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J266" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K266" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L266" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M266" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>ENR-01</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Enrobe bitumineux (t)</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Bitume et routes</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Enrobés</v>
+      </c>
+      <c r="E267" t="str">
+        <v>t</v>
+      </c>
+      <c r="F267">
+        <v>95000</v>
+      </c>
+      <c r="G267" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H267" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I267" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J267" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K267" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L267" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M267" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>ASP-01</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Asphalte (t)</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Bitume et routes</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Enrobés</v>
+      </c>
+      <c r="E268" t="str">
+        <v>t</v>
+      </c>
+      <c r="F268">
+        <v>98000</v>
+      </c>
+      <c r="G268" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H268" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J268" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K268" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L268" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M268" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>COU-01</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Couverture (m2)</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Couverture</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Toiture</v>
+      </c>
+      <c r="E269" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F269">
+        <v>9000</v>
+      </c>
+      <c r="G269" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H269" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I269" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J269" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K269" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L269" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M269" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>ETN-01</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Etancheite (m2)</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Couverture</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Étanchéité</v>
+      </c>
+      <c r="E270" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F270">
+        <v>6000</v>
+      </c>
+      <c r="G270" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H270" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J270" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K270" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L270" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M270" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>MEM-01</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Membrane etancheite (m2)</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Couverture</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Étanchéité</v>
+      </c>
+      <c r="E271" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F271">
+        <v>6000</v>
+      </c>
+      <c r="G271" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H271" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J271" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K271" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L271" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M271" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>SOT-01</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Sous-toiture (m2)</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Couverture</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Toiture</v>
+      </c>
+      <c r="E272" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F272">
+        <v>7500</v>
+      </c>
+      <c r="G272" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H272" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J272" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K272" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L272" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M272" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>BRD-01</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Bardage (m2)</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Bois et coffrage</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Charpente</v>
+      </c>
+      <c r="E273" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F273">
+        <v>8000</v>
+      </c>
+      <c r="G273" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H273" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J273" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K273" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L273" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M273" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>CAR-01</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Carrelage (m2)</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Revêtement sol</v>
+      </c>
+      <c r="E274" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F274">
+        <v>12000</v>
+      </c>
+      <c r="G274" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H274" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I274" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J274" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K274" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L274" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M274" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>CRU-01</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Carreau (u)</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Revêtement sol</v>
+      </c>
+      <c r="E275" t="str">
+        <v>u</v>
+      </c>
+      <c r="F275">
+        <v>800</v>
+      </c>
+      <c r="G275" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H275" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I275" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J275" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K275" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L275" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M275" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FAI-01</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Faience (m2)</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Revêtement mural</v>
+      </c>
+      <c r="E276" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F276">
+        <v>11000</v>
+      </c>
+      <c r="G276" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H276" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J276" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K276" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L276" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M276" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>COL-01</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Colle a carrelage (kg)</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Colles</v>
+      </c>
+      <c r="E277" t="str">
+        <v>kg</v>
+      </c>
+      <c r="F277">
+        <v>5000</v>
+      </c>
+      <c r="G277" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H277" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I277" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J277" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K277" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L277" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M277" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>MTC-01</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Mortier colle (kg)</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Colles</v>
+      </c>
+      <c r="E278" t="str">
+        <v>kg</v>
+      </c>
+      <c r="F278">
+        <v>4500</v>
+      </c>
+      <c r="G278" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H278" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I278" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J278" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K278" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L278" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M278" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>CHP-01</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Chape (m3)</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Chape</v>
+      </c>
+      <c r="E279" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F279">
+        <v>95000</v>
+      </c>
+      <c r="G279" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H279" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J279" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K279" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L279" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M279" t="str">
+        <v>Prix estimé à confirmer</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>RGR-01</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Ragreage (m2)</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Finitions</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Ragréage</v>
+      </c>
+      <c r="E280" t="str">
+        <v>m2</v>
+      </c>
+      <c r="F280">
+        <v>8000</v>
+      </c>
+      <c r="G280" t="str">
+        <v>Abidjan</v>
+      </c>
+      <c r="H280" t="str">
+        <v>Marché ivoirien</v>
+      </c>
+      <c r="I280" t="str">
+        <v>Marché ivoirien 2026 (estimation) - à vérifier</v>
+      </c>
+      <c r="J280" t="str">
+        <v>14/10/2026</v>
+      </c>
+      <c r="K280" t="str">
+        <v>16/04/2027</v>
+      </c>
+      <c r="L280" t="str">
+        <v>a_verifier</v>
+      </c>
+      <c r="M280" t="str">
         <v>Prix estimé à confirmer</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M260"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M280"/>
   </ignoredErrors>
 </worksheet>
 </file>